--- a/output/yearly_population_iteration_86_growth_param_0.5.xlsx
+++ b/output/yearly_population_iteration_86_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6271</v>
+        <v>6197</v>
       </c>
       <c r="C2" t="n">
-        <v>7970</v>
+        <v>12366</v>
       </c>
       <c r="D2" t="n">
-        <v>22391</v>
+        <v>26119</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4268</v>
+        <v>3918</v>
       </c>
       <c r="C3" t="n">
-        <v>7816</v>
+        <v>8739</v>
       </c>
       <c r="D3" t="n">
-        <v>9481</v>
+        <v>15826</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3081</v>
+        <v>2797</v>
       </c>
       <c r="C4" t="n">
-        <v>4762</v>
+        <v>6481</v>
       </c>
       <c r="D4" t="n">
-        <v>4555</v>
+        <v>6408</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1978</v>
+        <v>1863</v>
       </c>
       <c r="C5" t="n">
-        <v>4798</v>
+        <v>5124</v>
       </c>
       <c r="D5" t="n">
-        <v>1841</v>
+        <v>2247</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1113</v>
+        <v>1097</v>
       </c>
       <c r="C6" t="n">
-        <v>3709</v>
+        <v>4153</v>
       </c>
       <c r="D6" t="n">
-        <v>955</v>
+        <v>994</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>541</v>
+        <v>524</v>
       </c>
       <c r="C7" t="n">
-        <v>2485</v>
+        <v>3099</v>
       </c>
       <c r="D7" t="n">
-        <v>628</v>
+        <v>622</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C8" t="n">
-        <v>1235</v>
+        <v>1605</v>
       </c>
       <c r="D8" t="n">
-        <v>427</v>
+        <v>422</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="C9" t="n">
-        <v>485</v>
+        <v>580</v>
       </c>
       <c r="D9" t="n">
-        <v>307</v>
+        <v>304</v>
       </c>
     </row>
     <row r="10">
@@ -892,10 +892,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C10" t="n">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="D10" t="n">
         <v>244</v>
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C11" t="n">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D11" t="n">
-        <v>202</v>
+        <v>198</v>
       </c>
     </row>
     <row r="12">
@@ -923,10 +923,10 @@
         <v>17</v>
       </c>
       <c r="C12" t="n">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="D12" t="n">
-        <v>162</v>
+        <v>158</v>
       </c>
     </row>
     <row r="13">
@@ -934,13 +934,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C13" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D13" t="n">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="14">
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="D14" t="n">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="15">
@@ -962,13 +962,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C15" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="16">
@@ -979,7 +979,7 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D16" t="n">
         <v>65</v>
@@ -993,10 +993,10 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="18">
@@ -1010,7 +1010,7 @@
         <v>33</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
@@ -1035,7 +1035,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -1049,7 +1049,7 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D21" t="n">
         <v>8</v>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7436</v>
+        <v>6282</v>
       </c>
       <c r="C2" t="n">
-        <v>14992</v>
+        <v>13146</v>
       </c>
       <c r="D2" t="n">
-        <v>34180</v>
+        <v>28455</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4202</v>
+        <v>3953</v>
       </c>
       <c r="C3" t="n">
-        <v>6950</v>
+        <v>9080</v>
       </c>
       <c r="D3" t="n">
-        <v>10599</v>
+        <v>16105</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3065</v>
+        <v>2769</v>
       </c>
       <c r="C4" t="n">
-        <v>6053</v>
+        <v>7343</v>
       </c>
       <c r="D4" t="n">
-        <v>5220</v>
+        <v>7659</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2183</v>
+        <v>1983</v>
       </c>
       <c r="C5" t="n">
-        <v>4681</v>
+        <v>5541</v>
       </c>
       <c r="D5" t="n">
-        <v>2184</v>
+        <v>2756</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1342</v>
+        <v>1288</v>
       </c>
       <c r="C6" t="n">
-        <v>4117</v>
+        <v>4475</v>
       </c>
       <c r="D6" t="n">
-        <v>1078</v>
+        <v>1161</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>700</v>
+        <v>669</v>
       </c>
       <c r="C7" t="n">
-        <v>3023</v>
+        <v>3531</v>
       </c>
       <c r="D7" t="n">
-        <v>663</v>
+        <v>660</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>300</v>
+        <v>282</v>
       </c>
       <c r="C8" t="n">
-        <v>1749</v>
+        <v>2174</v>
       </c>
       <c r="D8" t="n">
-        <v>452</v>
+        <v>445</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="C9" t="n">
-        <v>793</v>
+        <v>971</v>
       </c>
       <c r="D9" t="n">
-        <v>317</v>
+        <v>312</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C10" t="n">
-        <v>328</v>
+        <v>357</v>
       </c>
       <c r="D10" t="n">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C11" t="n">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="D11" t="n">
-        <v>203</v>
+        <v>199</v>
       </c>
     </row>
     <row r="12">
@@ -1231,13 +1231,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C12" t="n">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="D12" t="n">
-        <v>165</v>
+        <v>161</v>
       </c>
     </row>
     <row r="13">
@@ -1248,10 +1248,10 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="D13" t="n">
-        <v>125</v>
+        <v>123</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="D14" t="n">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="15">
@@ -1273,10 +1273,10 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C15" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D15" t="n">
         <v>80</v>
@@ -1287,10 +1287,10 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C16" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D16" t="n">
         <v>65</v>
@@ -1307,7 +1307,7 @@
         <v>39</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="18">
@@ -1321,7 +1321,7 @@
         <v>33</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
@@ -1346,7 +1346,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -1360,7 +1360,7 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D21" t="n">
         <v>9</v>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8456</v>
+        <v>6624</v>
       </c>
       <c r="C2" t="n">
-        <v>10801</v>
+        <v>11539</v>
       </c>
       <c r="D2" t="n">
-        <v>31447</v>
+        <v>26123</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4456</v>
+        <v>3931</v>
       </c>
       <c r="C3" t="n">
-        <v>9013</v>
+        <v>9454</v>
       </c>
       <c r="D3" t="n">
-        <v>12750</v>
+        <v>16483</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2995</v>
+        <v>2725</v>
       </c>
       <c r="C4" t="n">
-        <v>6247</v>
+        <v>7803</v>
       </c>
       <c r="D4" t="n">
-        <v>5785</v>
+        <v>8487</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2251</v>
+        <v>2024</v>
       </c>
       <c r="C5" t="n">
-        <v>5105</v>
+        <v>6064</v>
       </c>
       <c r="D5" t="n">
-        <v>2554</v>
+        <v>3331</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1536</v>
+        <v>1407</v>
       </c>
       <c r="C6" t="n">
-        <v>4308</v>
+        <v>4837</v>
       </c>
       <c r="D6" t="n">
-        <v>1202</v>
+        <v>1333</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>849</v>
+        <v>801</v>
       </c>
       <c r="C7" t="n">
-        <v>3421</v>
+        <v>3837</v>
       </c>
       <c r="D7" t="n">
-        <v>713</v>
+        <v>717</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>398</v>
+        <v>370</v>
       </c>
       <c r="C8" t="n">
-        <v>2218</v>
+        <v>2630</v>
       </c>
       <c r="D8" t="n">
-        <v>469</v>
+        <v>461</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>154</v>
+        <v>142</v>
       </c>
       <c r="C9" t="n">
-        <v>1148</v>
+        <v>1373</v>
       </c>
       <c r="D9" t="n">
-        <v>330</v>
+        <v>324</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C10" t="n">
-        <v>488</v>
+        <v>561</v>
       </c>
       <c r="D10" t="n">
-        <v>252</v>
+        <v>250</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C11" t="n">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="D11" t="n">
-        <v>206</v>
+        <v>200</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C12" t="n">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="D12" t="n">
-        <v>165</v>
+        <v>163</v>
       </c>
     </row>
     <row r="13">
@@ -1559,10 +1559,10 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="D13" t="n">
-        <v>128</v>
+        <v>124</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="D14" t="n">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="15">
@@ -1584,13 +1584,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C15" t="n">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="D15" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="16">
@@ -1598,10 +1598,10 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C16" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D16" t="n">
         <v>65</v>
@@ -1612,13 +1612,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C17" t="n">
         <v>40</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="18">
@@ -1632,7 +1632,7 @@
         <v>34</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
@@ -1657,7 +1657,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -1671,10 +1671,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D21" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7799</v>
+        <v>6277</v>
       </c>
       <c r="C2" t="n">
-        <v>7431</v>
+        <v>8308</v>
       </c>
       <c r="D2" t="n">
-        <v>25769</v>
+        <v>21847</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5323</v>
+        <v>4699</v>
       </c>
       <c r="C3" t="n">
-        <v>12500</v>
+        <v>13519</v>
       </c>
       <c r="D3" t="n">
-        <v>13405</v>
+        <v>17562</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2079</v>
+        <v>1870</v>
       </c>
       <c r="C4" t="n">
-        <v>8259</v>
+        <v>9791</v>
       </c>
       <c r="D4" t="n">
-        <v>5541</v>
+        <v>7793</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1419</v>
+        <v>1300</v>
       </c>
       <c r="C5" t="n">
-        <v>4221</v>
+        <v>4740</v>
       </c>
       <c r="D5" t="n">
-        <v>1864</v>
+        <v>2169</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>784</v>
+        <v>740</v>
       </c>
       <c r="C6" t="n">
-        <v>3352</v>
+        <v>3760</v>
       </c>
       <c r="D6" t="n">
-        <v>698</v>
+        <v>702</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>367</v>
+        <v>341</v>
       </c>
       <c r="C7" t="n">
-        <v>2173</v>
+        <v>2577</v>
       </c>
       <c r="D7" t="n">
-        <v>459</v>
+        <v>451</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>142</v>
+        <v>131</v>
       </c>
       <c r="C8" t="n">
-        <v>1125</v>
+        <v>1345</v>
       </c>
       <c r="D8" t="n">
-        <v>323</v>
+        <v>317</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="C9" t="n">
-        <v>478</v>
+        <v>549</v>
       </c>
       <c r="D9" t="n">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C10" t="n">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="D10" t="n">
-        <v>201</v>
+        <v>196</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C11" t="n">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="D11" t="n">
-        <v>161</v>
+        <v>159</v>
       </c>
     </row>
     <row r="12">
@@ -1856,10 +1856,10 @@
         <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="D12" t="n">
-        <v>125</v>
+        <v>121</v>
       </c>
     </row>
     <row r="13">
@@ -1867,10 +1867,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C13" t="n">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="D13" t="n">
         <v>98</v>
@@ -1881,13 +1881,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C14" t="n">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="D14" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="15">
@@ -1895,7 +1895,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C15" t="n">
         <v>49</v>
@@ -1909,13 +1909,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
         <v>39</v>
       </c>
       <c r="D16" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="17">
@@ -1929,7 +1929,7 @@
         <v>33</v>
       </c>
       <c r="D17" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="18">
@@ -1954,7 +1954,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D19" t="n">
         <v>15</v>
@@ -1968,10 +1968,10 @@
         <v>8</v>
       </c>
       <c r="C20" t="n">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D20" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4819</v>
+        <v>3910</v>
       </c>
       <c r="C2" t="n">
-        <v>4200</v>
+        <v>4005</v>
       </c>
       <c r="D2" t="n">
-        <v>17819</v>
+        <v>15534</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5471</v>
+        <v>4620</v>
       </c>
       <c r="C3" t="n">
-        <v>9332</v>
+        <v>10328</v>
       </c>
       <c r="D3" t="n">
-        <v>14443</v>
+        <v>17295</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2842</v>
+        <v>2483</v>
       </c>
       <c r="C4" t="n">
-        <v>10238</v>
+        <v>11573</v>
       </c>
       <c r="D4" t="n">
-        <v>6558</v>
+        <v>8943</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1565</v>
+        <v>1419</v>
       </c>
       <c r="C5" t="n">
-        <v>5963</v>
+        <v>6714</v>
       </c>
       <c r="D5" t="n">
-        <v>2319</v>
+        <v>2792</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>935</v>
+        <v>860</v>
       </c>
       <c r="C6" t="n">
-        <v>3816</v>
+        <v>4302</v>
       </c>
       <c r="D6" t="n">
-        <v>810</v>
+        <v>840</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>343</v>
+        <v>314</v>
       </c>
       <c r="C7" t="n">
-        <v>2675</v>
+        <v>3056</v>
       </c>
       <c r="D7" t="n">
-        <v>496</v>
+        <v>491</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>117</v>
+        <v>107</v>
       </c>
       <c r="C8" t="n">
-        <v>1447</v>
+        <v>1725</v>
       </c>
       <c r="D8" t="n">
-        <v>332</v>
+        <v>326</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="C9" t="n">
-        <v>529</v>
+        <v>554</v>
       </c>
       <c r="D9" t="n">
-        <v>255</v>
+        <v>253</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C10" t="n">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="D10" t="n">
-        <v>210</v>
+        <v>205</v>
       </c>
     </row>
     <row r="11">
@@ -2153,10 +2153,10 @@
         <v>9</v>
       </c>
       <c r="C11" t="n">
-        <v>164</v>
+        <v>158</v>
       </c>
       <c r="D11" t="n">
-        <v>167</v>
+        <v>163</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C12" t="n">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="D12" t="n">
-        <v>131</v>
+        <v>129</v>
       </c>
     </row>
     <row r="13">
@@ -2178,13 +2178,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="D13" t="n">
-        <v>98</v>
+        <v>96</v>
       </c>
     </row>
     <row r="14">
@@ -2192,7 +2192,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
         <v>48</v>
@@ -2212,7 +2212,7 @@
         <v>38</v>
       </c>
       <c r="D15" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="16">
@@ -2226,7 +2226,7 @@
         <v>32</v>
       </c>
       <c r="D16" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="17">
@@ -2251,7 +2251,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D18" t="n">
         <v>14</v>
@@ -2265,10 +2265,10 @@
         <v>7</v>
       </c>
       <c r="C19" t="n">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D19" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5589</v>
+        <v>3873</v>
       </c>
       <c r="C2" t="n">
-        <v>14675</v>
+        <v>5528</v>
       </c>
       <c r="D2" t="n">
-        <v>15003</v>
+        <v>22892</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4369</v>
+        <v>3691</v>
       </c>
       <c r="C3" t="n">
-        <v>6192</v>
+        <v>6693</v>
       </c>
       <c r="D3" t="n">
-        <v>13931</v>
+        <v>15935</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3412</v>
+        <v>2849</v>
       </c>
       <c r="C4" t="n">
-        <v>9590</v>
+        <v>10869</v>
       </c>
       <c r="D4" t="n">
-        <v>7645</v>
+        <v>9954</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1860</v>
+        <v>1640</v>
       </c>
       <c r="C5" t="n">
-        <v>7808</v>
+        <v>8673</v>
       </c>
       <c r="D5" t="n">
-        <v>2899</v>
+        <v>3592</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1093</v>
+        <v>988</v>
       </c>
       <c r="C6" t="n">
-        <v>4764</v>
+        <v>5258</v>
       </c>
       <c r="D6" t="n">
-        <v>1016</v>
+        <v>1091</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>504</v>
+        <v>453</v>
       </c>
       <c r="C7" t="n">
-        <v>3180</v>
+        <v>3585</v>
       </c>
       <c r="D7" t="n">
-        <v>534</v>
+        <v>530</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>170</v>
+        <v>152</v>
       </c>
       <c r="C8" t="n">
-        <v>1941</v>
+        <v>2236</v>
       </c>
       <c r="D8" t="n">
-        <v>349</v>
+        <v>342</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="C9" t="n">
-        <v>866</v>
+        <v>960</v>
       </c>
       <c r="D9" t="n">
-        <v>263</v>
+        <v>258</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="C10" t="n">
         <v>342</v>
       </c>
       <c r="D10" t="n">
-        <v>212</v>
+        <v>209</v>
       </c>
     </row>
     <row r="11">
@@ -2464,10 +2464,10 @@
         <v>9</v>
       </c>
       <c r="C11" t="n">
-        <v>190</v>
+        <v>183</v>
       </c>
       <c r="D11" t="n">
-        <v>170</v>
+        <v>166</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C12" t="n">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="D12" t="n">
-        <v>133</v>
+        <v>130</v>
       </c>
     </row>
     <row r="13">
@@ -2489,13 +2489,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D13" t="n">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="14">
@@ -2506,10 +2506,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D14" t="n">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="15">
@@ -2520,10 +2520,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D15" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="16">
@@ -2537,7 +2537,7 @@
         <v>34</v>
       </c>
       <c r="D16" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="17">
@@ -2562,7 +2562,7 @@
         <v>6</v>
       </c>
       <c r="C18" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D18" t="n">
         <v>13</v>
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D19" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3347</v>
+        <v>2378</v>
       </c>
       <c r="C2" t="n">
-        <v>6989</v>
+        <v>2776</v>
       </c>
       <c r="D2" t="n">
-        <v>10471</v>
+        <v>16124</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4527</v>
+        <v>3635</v>
       </c>
       <c r="C3" t="n">
-        <v>8796</v>
+        <v>6178</v>
       </c>
       <c r="D3" t="n">
-        <v>13730</v>
+        <v>16271</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3714</v>
+        <v>3090</v>
       </c>
       <c r="C4" t="n">
-        <v>9234</v>
+        <v>10483</v>
       </c>
       <c r="D4" t="n">
-        <v>8350</v>
+        <v>10657</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1933</v>
+        <v>1705</v>
       </c>
       <c r="C5" t="n">
-        <v>9456</v>
+        <v>10501</v>
       </c>
       <c r="D5" t="n">
-        <v>3084</v>
+        <v>3698</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>899</v>
+        <v>792</v>
       </c>
       <c r="C6" t="n">
-        <v>5701</v>
+        <v>6120</v>
       </c>
       <c r="D6" t="n">
-        <v>1016</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>157</v>
+        <v>140</v>
       </c>
       <c r="C7" t="n">
-        <v>3388</v>
+        <v>3826</v>
       </c>
       <c r="D7" t="n">
-        <v>542</v>
+        <v>535</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="C8" t="n">
-        <v>1419</v>
+        <v>1554</v>
       </c>
       <c r="D8" t="n">
-        <v>371</v>
+        <v>363</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C9" t="n">
         <v>335</v>
       </c>
       <c r="D9" t="n">
-        <v>285</v>
+        <v>278</v>
       </c>
     </row>
     <row r="10">
@@ -2761,10 +2761,10 @@
         <v>8</v>
       </c>
       <c r="C10" t="n">
-        <v>186</v>
+        <v>179</v>
       </c>
       <c r="D10" t="n">
-        <v>166</v>
+        <v>162</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="D11" t="n">
-        <v>130</v>
+        <v>127</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="D12" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="13">
@@ -2803,10 +2803,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D13" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="14">
@@ -2817,10 +2817,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D14" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="15">
@@ -2834,7 +2834,7 @@
         <v>33</v>
       </c>
       <c r="D15" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="16">
@@ -2859,7 +2859,7 @@
         <v>5</v>
       </c>
       <c r="C17" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D17" t="n">
         <v>12</v>
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D18" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3521</v>
+        <v>3567</v>
       </c>
       <c r="C2" t="n">
-        <v>8368</v>
+        <v>3864</v>
       </c>
       <c r="D2" t="n">
-        <v>16085</v>
+        <v>13573</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3462</v>
+        <v>2705</v>
       </c>
       <c r="C3" t="n">
-        <v>7130</v>
+        <v>4246</v>
       </c>
       <c r="D3" t="n">
-        <v>12495</v>
+        <v>15341</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3522</v>
+        <v>2878</v>
       </c>
       <c r="C4" t="n">
-        <v>8928</v>
+        <v>8363</v>
       </c>
       <c r="D4" t="n">
-        <v>8922</v>
+        <v>11141</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2339</v>
+        <v>1987</v>
       </c>
       <c r="C5" t="n">
-        <v>9163</v>
+        <v>10375</v>
       </c>
       <c r="D5" t="n">
-        <v>3748</v>
+        <v>4520</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1168</v>
+        <v>1013</v>
       </c>
       <c r="C6" t="n">
-        <v>7311</v>
+        <v>7851</v>
       </c>
       <c r="D6" t="n">
-        <v>1290</v>
+        <v>1388</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>330</v>
+        <v>280</v>
       </c>
       <c r="C7" t="n">
-        <v>4303</v>
+        <v>4753</v>
       </c>
       <c r="D7" t="n">
-        <v>592</v>
+        <v>598</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>72</v>
+        <v>62</v>
       </c>
       <c r="C8" t="n">
-        <v>2140</v>
+        <v>2340</v>
       </c>
       <c r="D8" t="n">
-        <v>389</v>
+        <v>379</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="C9" t="n">
-        <v>684</v>
+        <v>703</v>
       </c>
       <c r="D9" t="n">
-        <v>292</v>
+        <v>284</v>
       </c>
     </row>
     <row r="10">
@@ -3072,10 +3072,10 @@
         <v>8</v>
       </c>
       <c r="C10" t="n">
-        <v>232</v>
+        <v>222</v>
       </c>
       <c r="D10" t="n">
-        <v>175</v>
+        <v>168</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C11" t="n">
-        <v>131</v>
+        <v>122</v>
       </c>
       <c r="D11" t="n">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="D12" t="n">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="13">
@@ -3114,10 +3114,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D13" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D14" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="15">
@@ -3145,7 +3145,7 @@
         <v>36</v>
       </c>
       <c r="D15" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="16">
@@ -3156,7 +3156,7 @@
         <v>4</v>
       </c>
       <c r="C16" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D16" t="n">
         <v>20</v>
@@ -3187,7 +3187,7 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2416</v>
+        <v>2386</v>
       </c>
       <c r="C2" t="n">
-        <v>4532</v>
+        <v>2292</v>
       </c>
       <c r="D2" t="n">
-        <v>11902</v>
+        <v>10056</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3051</v>
+        <v>2595</v>
       </c>
       <c r="C3" t="n">
-        <v>6985</v>
+        <v>3753</v>
       </c>
       <c r="D3" t="n">
-        <v>12237</v>
+        <v>14332</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3225</v>
+        <v>2583</v>
       </c>
       <c r="C4" t="n">
-        <v>8223</v>
+        <v>6888</v>
       </c>
       <c r="D4" t="n">
-        <v>9182</v>
+        <v>11540</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2553</v>
+        <v>2142</v>
       </c>
       <c r="C5" t="n">
-        <v>9243</v>
+        <v>9801</v>
       </c>
       <c r="D5" t="n">
-        <v>4252</v>
+        <v>5061</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1344</v>
+        <v>1145</v>
       </c>
       <c r="C6" t="n">
-        <v>8155</v>
+        <v>8889</v>
       </c>
       <c r="D6" t="n">
-        <v>1488</v>
+        <v>1652</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>296</v>
+        <v>249</v>
       </c>
       <c r="C7" t="n">
-        <v>5274</v>
+        <v>5745</v>
       </c>
       <c r="D7" t="n">
-        <v>649</v>
+        <v>655</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="C8" t="n">
-        <v>2664</v>
+        <v>2901</v>
       </c>
       <c r="D8" t="n">
-        <v>404</v>
+        <v>384</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C9" t="n">
-        <v>745</v>
+        <v>740</v>
       </c>
       <c r="D9" t="n">
-        <v>288</v>
+        <v>281</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C10" t="n">
-        <v>234</v>
+        <v>219</v>
       </c>
       <c r="D10" t="n">
-        <v>180</v>
+        <v>172</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>128</v>
+        <v>119</v>
       </c>
       <c r="D11" t="n">
-        <v>135</v>
+        <v>133</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="D12" t="n">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="13">
@@ -3425,10 +3425,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D13" t="n">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="14">
@@ -3442,7 +3442,7 @@
         <v>35</v>
       </c>
       <c r="D14" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="15">
@@ -3453,7 +3453,7 @@
         <v>3</v>
       </c>
       <c r="C15" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D15" t="n">
         <v>19</v>
@@ -3484,7 +3484,7 @@
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3086</v>
+        <v>3610</v>
       </c>
       <c r="C2" t="n">
-        <v>8563</v>
+        <v>6581</v>
       </c>
       <c r="D2" t="n">
-        <v>18253</v>
+        <v>17469</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2392</v>
+        <v>2130</v>
       </c>
       <c r="C3" t="n">
-        <v>5448</v>
+        <v>2877</v>
       </c>
       <c r="D3" t="n">
-        <v>11531</v>
+        <v>12958</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2752</v>
+        <v>2248</v>
       </c>
       <c r="C4" t="n">
-        <v>7552</v>
+        <v>5510</v>
       </c>
       <c r="D4" t="n">
-        <v>9225</v>
+        <v>11564</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2530</v>
+        <v>2107</v>
       </c>
       <c r="C5" t="n">
-        <v>8659</v>
+        <v>8506</v>
       </c>
       <c r="D5" t="n">
-        <v>4785</v>
+        <v>5715</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1614</v>
+        <v>1337</v>
       </c>
       <c r="C6" t="n">
-        <v>8486</v>
+        <v>9143</v>
       </c>
       <c r="D6" t="n">
-        <v>1813</v>
+        <v>2007</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>543</v>
+        <v>452</v>
       </c>
       <c r="C7" t="n">
-        <v>6288</v>
+        <v>6821</v>
       </c>
       <c r="D7" t="n">
-        <v>741</v>
+        <v>765</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>107</v>
+        <v>89</v>
       </c>
       <c r="C8" t="n">
-        <v>3532</v>
+        <v>3848</v>
       </c>
       <c r="D8" t="n">
-        <v>426</v>
+        <v>409</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C9" t="n">
-        <v>1353</v>
+        <v>1375</v>
       </c>
       <c r="D9" t="n">
-        <v>296</v>
+        <v>290</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C10" t="n">
-        <v>381</v>
+        <v>364</v>
       </c>
       <c r="D10" t="n">
-        <v>189</v>
+        <v>178</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>157</v>
+        <v>145</v>
       </c>
       <c r="D11" t="n">
-        <v>136</v>
+        <v>134</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="D12" t="n">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="13">
@@ -3739,7 +3739,7 @@
         <v>48</v>
       </c>
       <c r="D13" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="14">
@@ -3753,7 +3753,7 @@
         <v>37</v>
       </c>
       <c r="D14" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="15">
@@ -3764,7 +3764,7 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D15" t="n">
         <v>18</v>
@@ -3778,7 +3778,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="D16" t="n">
         <v>7</v>
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6809</v>
+        <v>7941</v>
       </c>
       <c r="C2" t="n">
-        <v>12524</v>
+        <v>19492</v>
       </c>
       <c r="D2" t="n">
-        <v>5027</v>
+        <v>3106</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2259</v>
+        <v>2664</v>
       </c>
       <c r="C2" t="n">
-        <v>5069</v>
+        <v>3949</v>
       </c>
       <c r="D2" t="n">
-        <v>13580</v>
+        <v>12996</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3174</v>
+        <v>2811</v>
       </c>
       <c r="C3" t="n">
-        <v>6665</v>
+        <v>3990</v>
       </c>
       <c r="D3" t="n">
-        <v>12800</v>
+        <v>14306</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3744</v>
+        <v>3096</v>
       </c>
       <c r="C4" t="n">
-        <v>10505</v>
+        <v>8316</v>
       </c>
       <c r="D4" t="n">
-        <v>9295</v>
+        <v>11639</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1514</v>
+        <v>1235</v>
       </c>
       <c r="C5" t="n">
-        <v>12222</v>
+        <v>12663</v>
       </c>
       <c r="D5" t="n">
-        <v>4351</v>
+        <v>5063</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>501</v>
+        <v>417</v>
       </c>
       <c r="C6" t="n">
-        <v>7659</v>
+        <v>8207</v>
       </c>
       <c r="D6" t="n">
-        <v>1509</v>
+        <v>1623</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>98</v>
+        <v>82</v>
       </c>
       <c r="C7" t="n">
-        <v>3461</v>
+        <v>3771</v>
       </c>
       <c r="D7" t="n">
-        <v>504</v>
+        <v>490</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C8" t="n">
-        <v>1325</v>
+        <v>1347</v>
       </c>
       <c r="D8" t="n">
-        <v>290</v>
+        <v>284</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C9" t="n">
-        <v>373</v>
+        <v>356</v>
       </c>
       <c r="D9" t="n">
-        <v>185</v>
+        <v>174</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>153</v>
+        <v>142</v>
       </c>
       <c r="D10" t="n">
-        <v>133</v>
+        <v>131</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="D11" t="n">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="12">
@@ -4347,7 +4347,7 @@
         <v>47</v>
       </c>
       <c r="D12" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="13">
@@ -4361,7 +4361,7 @@
         <v>36</v>
       </c>
       <c r="D13" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="14">
@@ -4372,7 +4372,7 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D14" t="n">
         <v>17</v>
@@ -4386,7 +4386,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D15" t="n">
         <v>6</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7387</v>
+        <v>7977</v>
       </c>
       <c r="C2" t="n">
-        <v>7487</v>
+        <v>12209</v>
       </c>
       <c r="D2" t="n">
-        <v>9181</v>
+        <v>17827</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2892</v>
+        <v>3372</v>
       </c>
       <c r="C3" t="n">
-        <v>6312</v>
+        <v>9823</v>
       </c>
       <c r="D3" t="n">
-        <v>1483</v>
+        <v>1161</v>
       </c>
     </row>
     <row r="4">
@@ -4557,7 +4557,7 @@
         <v>193</v>
       </c>
       <c r="C5" t="n">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="D5" t="n">
         <v>1161</v>
@@ -4571,7 +4571,7 @@
         <v>200</v>
       </c>
       <c r="C6" t="n">
-        <v>459</v>
+        <v>454</v>
       </c>
       <c r="D6" t="n">
         <v>816</v>
@@ -4596,7 +4596,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C8" t="n">
         <v>260</v>
@@ -4610,7 +4610,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C9" t="n">
         <v>205</v>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5660</v>
+        <v>5594</v>
       </c>
       <c r="C2" t="n">
-        <v>7857</v>
+        <v>5234</v>
       </c>
       <c r="D2" t="n">
-        <v>11744</v>
+        <v>15873</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4221</v>
+        <v>4627</v>
       </c>
       <c r="C3" t="n">
-        <v>6016</v>
+        <v>9730</v>
       </c>
       <c r="D3" t="n">
-        <v>2667</v>
+        <v>3743</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1290</v>
+        <v>1470</v>
       </c>
       <c r="C4" t="n">
-        <v>3742</v>
+        <v>5704</v>
       </c>
       <c r="D4" t="n">
-        <v>1480</v>
+        <v>1404</v>
       </c>
     </row>
     <row r="5">
@@ -4865,10 +4865,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="C5" t="n">
-        <v>219</v>
+        <v>225</v>
       </c>
       <c r="D5" t="n">
         <v>1198</v>
@@ -4879,7 +4879,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="C6" t="n">
         <v>410</v>
@@ -4893,10 +4893,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C7" t="n">
-        <v>409</v>
+        <v>405</v>
       </c>
       <c r="D7" t="n">
         <v>584</v>
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C8" t="n">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="D8" t="n">
-        <v>439</v>
+        <v>443</v>
       </c>
     </row>
     <row r="9">
@@ -4924,10 +4924,10 @@
         <v>85</v>
       </c>
       <c r="C9" t="n">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="D9" t="n">
-        <v>363</v>
+        <v>359</v>
       </c>
     </row>
     <row r="10">
@@ -4949,10 +4949,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C11" t="n">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="D11" t="n">
         <v>270</v>
@@ -4966,7 +4966,7 @@
         <v>28</v>
       </c>
       <c r="C12" t="n">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D12" t="n">
         <v>206</v>
@@ -4994,7 +4994,7 @@
         <v>15</v>
       </c>
       <c r="C14" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D14" t="n">
         <v>146</v>
@@ -5005,7 +5005,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C15" t="n">
         <v>74</v>
@@ -5025,7 +5025,7 @@
         <v>71</v>
       </c>
       <c r="D16" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="17">
@@ -5036,10 +5036,10 @@
         <v>12</v>
       </c>
       <c r="C17" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="18">
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4955</v>
+        <v>5032</v>
       </c>
       <c r="C2" t="n">
-        <v>5761</v>
+        <v>3715</v>
       </c>
       <c r="D2" t="n">
-        <v>10524</v>
+        <v>18721</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4052</v>
+        <v>4198</v>
       </c>
       <c r="C3" t="n">
-        <v>6134</v>
+        <v>6403</v>
       </c>
       <c r="D3" t="n">
-        <v>3927</v>
+        <v>5323</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2344</v>
+        <v>2568</v>
       </c>
       <c r="C4" t="n">
-        <v>4894</v>
+        <v>7733</v>
       </c>
       <c r="D4" t="n">
-        <v>1662</v>
+        <v>1774</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>578</v>
+        <v>640</v>
       </c>
       <c r="C5" t="n">
-        <v>2142</v>
+        <v>3165</v>
       </c>
       <c r="D5" t="n">
-        <v>1201</v>
+        <v>1199</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C6" t="n">
-        <v>304</v>
+        <v>309</v>
       </c>
       <c r="D6" t="n">
-        <v>908</v>
+        <v>897</v>
       </c>
     </row>
     <row r="7">
@@ -5207,7 +5207,7 @@
         <v>158</v>
       </c>
       <c r="C7" t="n">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="D7" t="n">
         <v>626</v>
@@ -5221,10 +5221,10 @@
         <v>125</v>
       </c>
       <c r="C8" t="n">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="D8" t="n">
-        <v>454</v>
+        <v>457</v>
       </c>
     </row>
     <row r="9">
@@ -5235,10 +5235,10 @@
         <v>90</v>
       </c>
       <c r="C9" t="n">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="D9" t="n">
-        <v>371</v>
+        <v>369</v>
       </c>
     </row>
     <row r="10">
@@ -5249,10 +5249,10 @@
         <v>66</v>
       </c>
       <c r="C10" t="n">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="D10" t="n">
-        <v>346</v>
+        <v>349</v>
       </c>
     </row>
     <row r="11">
@@ -5263,10 +5263,10 @@
         <v>46</v>
       </c>
       <c r="C11" t="n">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="D11" t="n">
-        <v>280</v>
+        <v>276</v>
       </c>
     </row>
     <row r="12">
@@ -5291,7 +5291,7 @@
         <v>21</v>
       </c>
       <c r="C13" t="n">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D13" t="n">
         <v>173</v>
@@ -5305,7 +5305,7 @@
         <v>15</v>
       </c>
       <c r="C14" t="n">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="D14" t="n">
         <v>148</v>
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D15" t="n">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="16">
@@ -5347,10 +5347,10 @@
         <v>11</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D17" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="18">
@@ -5364,7 +5364,7 @@
         <v>65</v>
       </c>
       <c r="D18" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="19">
@@ -5375,7 +5375,7 @@
         <v>10</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D19" t="n">
         <v>41</v>
@@ -5403,7 +5403,7 @@
         <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D21" t="n">
         <v>5</v>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6028</v>
+        <v>6105</v>
       </c>
       <c r="C2" t="n">
-        <v>8743</v>
+        <v>9769</v>
       </c>
       <c r="D2" t="n">
-        <v>19250</v>
+        <v>28241</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3687</v>
+        <v>3778</v>
       </c>
       <c r="C3" t="n">
-        <v>5171</v>
+        <v>4432</v>
       </c>
       <c r="D3" t="n">
-        <v>4653</v>
+        <v>6886</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2686</v>
+        <v>2834</v>
       </c>
       <c r="C4" t="n">
-        <v>5458</v>
+        <v>6882</v>
       </c>
       <c r="D4" t="n">
-        <v>2024</v>
+        <v>2316</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1203</v>
+        <v>1305</v>
       </c>
       <c r="C5" t="n">
-        <v>3524</v>
+        <v>5349</v>
       </c>
       <c r="D5" t="n">
-        <v>1232</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>308</v>
+        <v>329</v>
       </c>
       <c r="C6" t="n">
-        <v>1215</v>
+        <v>1704</v>
       </c>
       <c r="D6" t="n">
-        <v>946</v>
+        <v>925</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="C7" t="n">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="D7" t="n">
-        <v>660</v>
+        <v>664</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C8" t="n">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="D8" t="n">
-        <v>478</v>
+        <v>474</v>
       </c>
     </row>
     <row r="9">
@@ -5549,7 +5549,7 @@
         <v>306</v>
       </c>
       <c r="D9" t="n">
-        <v>380</v>
+        <v>379</v>
       </c>
     </row>
     <row r="10">
@@ -5560,10 +5560,10 @@
         <v>70</v>
       </c>
       <c r="C10" t="n">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="D10" t="n">
-        <v>342</v>
+        <v>348</v>
       </c>
     </row>
     <row r="11">
@@ -5577,7 +5577,7 @@
         <v>189</v>
       </c>
       <c r="D11" t="n">
-        <v>286</v>
+        <v>280</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C12" t="n">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="D12" t="n">
-        <v>217</v>
+        <v>219</v>
       </c>
     </row>
     <row r="13">
@@ -5602,10 +5602,10 @@
         <v>22</v>
       </c>
       <c r="C13" t="n">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="D13" t="n">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="14">
@@ -5616,10 +5616,10 @@
         <v>15</v>
       </c>
       <c r="C14" t="n">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D14" t="n">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="15">
@@ -5689,7 +5689,7 @@
         <v>62</v>
       </c>
       <c r="D19" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="20">
@@ -5700,7 +5700,7 @@
         <v>7</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D20" t="n">
         <v>24</v>
@@ -5714,7 +5714,7 @@
         <v>21</v>
       </c>
       <c r="C21" t="n">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="D21" t="n">
         <v>7</v>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7843</v>
+        <v>6254</v>
       </c>
       <c r="C2" t="n">
-        <v>7662</v>
+        <v>9117</v>
       </c>
       <c r="D2" t="n">
-        <v>20689</v>
+        <v>33059</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3504</v>
+        <v>3522</v>
       </c>
       <c r="C3" t="n">
-        <v>5706</v>
+        <v>5746</v>
       </c>
       <c r="D3" t="n">
-        <v>6156</v>
+        <v>8912</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1981</v>
+        <v>2020</v>
       </c>
       <c r="C4" t="n">
-        <v>4296</v>
+        <v>4519</v>
       </c>
       <c r="D4" t="n">
-        <v>2128</v>
+        <v>2625</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1005</v>
+        <v>1070</v>
       </c>
       <c r="C5" t="n">
-        <v>3303</v>
+        <v>4448</v>
       </c>
       <c r="D5" t="n">
-        <v>1069</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>355</v>
+        <v>371</v>
       </c>
       <c r="C6" t="n">
-        <v>1578</v>
+        <v>2298</v>
       </c>
       <c r="D6" t="n">
-        <v>757</v>
+        <v>737</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="C7" t="n">
-        <v>494</v>
+        <v>628</v>
       </c>
       <c r="D7" t="n">
-        <v>513</v>
+        <v>518</v>
       </c>
     </row>
     <row r="8">
@@ -5843,10 +5843,10 @@
         <v>58</v>
       </c>
       <c r="C8" t="n">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="D8" t="n">
-        <v>360</v>
+        <v>357</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C9" t="n">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="D9" t="n">
-        <v>273</v>
+        <v>269</v>
       </c>
     </row>
     <row r="10">
@@ -5871,10 +5871,10 @@
         <v>30</v>
       </c>
       <c r="C10" t="n">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="D10" t="n">
-        <v>233</v>
+        <v>238</v>
       </c>
     </row>
     <row r="11">
@@ -5888,7 +5888,7 @@
         <v>114</v>
       </c>
       <c r="D11" t="n">
-        <v>195</v>
+        <v>190</v>
       </c>
     </row>
     <row r="12">
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C12" t="n">
         <v>91</v>
       </c>
       <c r="D12" t="n">
-        <v>147</v>
+        <v>149</v>
       </c>
     </row>
     <row r="13">
@@ -5910,13 +5910,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C13" t="n">
         <v>73</v>
       </c>
       <c r="D13" t="n">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="14">
@@ -5927,10 +5927,10 @@
         <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D14" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="15">
@@ -5941,10 +5941,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="16">
@@ -5958,7 +5958,7 @@
         <v>38</v>
       </c>
       <c r="D16" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17">
@@ -6011,7 +6011,7 @@
         <v>2</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D20" t="n">
         <v>15</v>
@@ -6025,7 +6025,7 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D21" t="n">
         <v>5</v>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5499</v>
+        <v>5867</v>
       </c>
       <c r="C2" t="n">
-        <v>4406</v>
+        <v>10671</v>
       </c>
       <c r="D2" t="n">
-        <v>17983</v>
+        <v>28048</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4695</v>
+        <v>4052</v>
       </c>
       <c r="C3" t="n">
-        <v>5888</v>
+        <v>6600</v>
       </c>
       <c r="D3" t="n">
-        <v>8144</v>
+        <v>12398</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2379</v>
+        <v>2378</v>
       </c>
       <c r="C4" t="n">
-        <v>5059</v>
+        <v>5143</v>
       </c>
       <c r="D4" t="n">
-        <v>2854</v>
+        <v>3727</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1334</v>
+        <v>1367</v>
       </c>
       <c r="C5" t="n">
-        <v>3815</v>
+        <v>4395</v>
       </c>
       <c r="D5" t="n">
-        <v>1249</v>
+        <v>1388</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>628</v>
+        <v>649</v>
       </c>
       <c r="C6" t="n">
-        <v>2535</v>
+        <v>3447</v>
       </c>
       <c r="D6" t="n">
-        <v>806</v>
+        <v>792</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>202</v>
+        <v>209</v>
       </c>
       <c r="C7" t="n">
-        <v>1099</v>
+        <v>1527</v>
       </c>
       <c r="D7" t="n">
-        <v>548</v>
+        <v>553</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C8" t="n">
-        <v>367</v>
+        <v>430</v>
       </c>
       <c r="D8" t="n">
-        <v>384</v>
+        <v>381</v>
       </c>
     </row>
     <row r="9">
@@ -6168,10 +6168,10 @@
         <v>46</v>
       </c>
       <c r="C9" t="n">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="D9" t="n">
-        <v>285</v>
+        <v>278</v>
       </c>
     </row>
     <row r="10">
@@ -6182,10 +6182,10 @@
         <v>33</v>
       </c>
       <c r="C10" t="n">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="D10" t="n">
-        <v>235</v>
+        <v>240</v>
       </c>
     </row>
     <row r="11">
@@ -6193,13 +6193,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C11" t="n">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="D11" t="n">
-        <v>199</v>
+        <v>193</v>
       </c>
     </row>
     <row r="12">
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C13" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D13" t="n">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="14">
@@ -6235,13 +6235,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C14" t="n">
         <v>63</v>
       </c>
       <c r="D14" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="15">
@@ -6252,7 +6252,7 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D15" t="n">
         <v>79</v>
@@ -6269,7 +6269,7 @@
         <v>40</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="17">
@@ -6280,10 +6280,10 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="18">
@@ -6297,7 +6297,7 @@
         <v>33</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
@@ -6322,10 +6322,10 @@
         <v>1</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="21">
@@ -6336,7 +6336,7 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D21" t="n">
         <v>6</v>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6397</v>
+        <v>5745</v>
       </c>
       <c r="C2" t="n">
-        <v>13578</v>
+        <v>12767</v>
       </c>
       <c r="D2" t="n">
-        <v>15929</v>
+        <v>34918</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4195</v>
+        <v>4023</v>
       </c>
       <c r="C3" t="n">
-        <v>4418</v>
+        <v>7568</v>
       </c>
       <c r="D3" t="n">
-        <v>9131</v>
+        <v>13903</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3034</v>
+        <v>2702</v>
       </c>
       <c r="C4" t="n">
-        <v>5366</v>
+        <v>5819</v>
       </c>
       <c r="D4" t="n">
-        <v>3782</v>
+        <v>5195</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1618</v>
+        <v>1631</v>
       </c>
       <c r="C5" t="n">
-        <v>4416</v>
+        <v>4691</v>
       </c>
       <c r="D5" t="n">
-        <v>1491</v>
+        <v>1736</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="C6" t="n">
-        <v>3181</v>
+        <v>3849</v>
       </c>
       <c r="D6" t="n">
-        <v>875</v>
+        <v>884</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="C7" t="n">
-        <v>1844</v>
+        <v>2486</v>
       </c>
       <c r="D7" t="n">
-        <v>587</v>
+        <v>581</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C8" t="n">
-        <v>729</v>
+        <v>956</v>
       </c>
       <c r="D8" t="n">
-        <v>403</v>
+        <v>405</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C9" t="n">
-        <v>286</v>
+        <v>308</v>
       </c>
       <c r="D9" t="n">
-        <v>298</v>
+        <v>291</v>
       </c>
     </row>
     <row r="10">
@@ -6493,10 +6493,10 @@
         <v>35</v>
       </c>
       <c r="C10" t="n">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="D10" t="n">
-        <v>238</v>
+        <v>240</v>
       </c>
     </row>
     <row r="11">
@@ -6504,13 +6504,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C11" t="n">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="D11" t="n">
-        <v>202</v>
+        <v>197</v>
       </c>
     </row>
     <row r="12">
@@ -6521,10 +6521,10 @@
         <v>16</v>
       </c>
       <c r="C12" t="n">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="D12" t="n">
-        <v>158</v>
+        <v>155</v>
       </c>
     </row>
     <row r="13">
@@ -6532,10 +6532,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C13" t="n">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D13" t="n">
         <v>121</v>
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D14" t="n">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="15">
@@ -6563,10 +6563,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="16">
@@ -6591,10 +6591,10 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="18">
@@ -6608,7 +6608,7 @@
         <v>33</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
@@ -6633,7 +6633,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -6647,7 +6647,7 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D21" t="n">
         <v>7</v>

--- a/output/yearly_population_iteration_86_growth_param_0.5.xlsx
+++ b/output/yearly_population_iteration_86_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6197</v>
+        <v>5993</v>
       </c>
       <c r="C2" t="n">
-        <v>12366</v>
+        <v>10233</v>
       </c>
       <c r="D2" t="n">
-        <v>26119</v>
+        <v>38585</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3918</v>
+        <v>3272</v>
       </c>
       <c r="C3" t="n">
-        <v>8739</v>
+        <v>5232</v>
       </c>
       <c r="D3" t="n">
-        <v>15826</v>
+        <v>21485</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2797</v>
+        <v>2738</v>
       </c>
       <c r="C4" t="n">
-        <v>6481</v>
+        <v>4778</v>
       </c>
       <c r="D4" t="n">
-        <v>6408</v>
+        <v>9706</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1863</v>
+        <v>1920</v>
       </c>
       <c r="C5" t="n">
-        <v>5124</v>
+        <v>2862</v>
       </c>
       <c r="D5" t="n">
-        <v>2247</v>
+        <v>3084</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1097</v>
+        <v>1121</v>
       </c>
       <c r="C6" t="n">
-        <v>4153</v>
+        <v>1777</v>
       </c>
       <c r="D6" t="n">
-        <v>994</v>
+        <v>1163</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>524</v>
+        <v>527</v>
       </c>
       <c r="C7" t="n">
-        <v>3099</v>
+        <v>1121</v>
       </c>
       <c r="D7" t="n">
-        <v>622</v>
+        <v>642</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="C8" t="n">
-        <v>1605</v>
+        <v>565</v>
       </c>
       <c r="D8" t="n">
-        <v>422</v>
+        <v>440</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C9" t="n">
-        <v>580</v>
+        <v>293</v>
       </c>
       <c r="D9" t="n">
-        <v>304</v>
+        <v>309</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C10" t="n">
-        <v>234</v>
+        <v>210</v>
       </c>
       <c r="D10" t="n">
-        <v>244</v>
+        <v>246</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C11" t="n">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="D11" t="n">
-        <v>198</v>
+        <v>206</v>
       </c>
     </row>
     <row r="12">
@@ -923,7 +923,7 @@
         <v>17</v>
       </c>
       <c r="C12" t="n">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="D12" t="n">
         <v>158</v>
@@ -934,13 +934,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="D13" t="n">
-        <v>122</v>
+        <v>125</v>
       </c>
     </row>
     <row r="14">
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C14" t="n">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="D14" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="15">
@@ -962,13 +962,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="16">
@@ -979,10 +979,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="17">
@@ -996,7 +996,7 @@
         <v>38</v>
       </c>
       <c r="D17" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18">
@@ -1007,7 +1007,7 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D18" t="n">
         <v>39</v>
@@ -1024,7 +1024,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="20">
@@ -1038,7 +1038,7 @@
         <v>29</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="21">
@@ -1049,10 +1049,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6282</v>
+        <v>8684</v>
       </c>
       <c r="C2" t="n">
-        <v>13146</v>
+        <v>6486</v>
       </c>
       <c r="D2" t="n">
-        <v>28455</v>
+        <v>40186</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3953</v>
+        <v>3650</v>
       </c>
       <c r="C3" t="n">
-        <v>9080</v>
+        <v>6636</v>
       </c>
       <c r="D3" t="n">
-        <v>16105</v>
+        <v>22366</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2769</v>
+        <v>2575</v>
       </c>
       <c r="C4" t="n">
-        <v>7343</v>
+        <v>4855</v>
       </c>
       <c r="D4" t="n">
-        <v>7659</v>
+        <v>11240</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1983</v>
+        <v>2020</v>
       </c>
       <c r="C5" t="n">
-        <v>5541</v>
+        <v>3722</v>
       </c>
       <c r="D5" t="n">
-        <v>2756</v>
+        <v>4070</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1288</v>
+        <v>1341</v>
       </c>
       <c r="C6" t="n">
-        <v>4475</v>
+        <v>2241</v>
       </c>
       <c r="D6" t="n">
-        <v>1161</v>
+        <v>1431</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>669</v>
+        <v>710</v>
       </c>
       <c r="C7" t="n">
-        <v>3531</v>
+        <v>1422</v>
       </c>
       <c r="D7" t="n">
-        <v>660</v>
+        <v>717</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>282</v>
+        <v>293</v>
       </c>
       <c r="C8" t="n">
-        <v>2174</v>
+        <v>804</v>
       </c>
       <c r="D8" t="n">
-        <v>445</v>
+        <v>460</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="C9" t="n">
-        <v>971</v>
+        <v>410</v>
       </c>
       <c r="D9" t="n">
-        <v>312</v>
+        <v>325</v>
       </c>
     </row>
     <row r="10">
@@ -1203,10 +1203,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="C10" t="n">
-        <v>357</v>
+        <v>244</v>
       </c>
       <c r="D10" t="n">
         <v>249</v>
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C11" t="n">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="D11" t="n">
-        <v>199</v>
+        <v>209</v>
       </c>
     </row>
     <row r="12">
@@ -1231,13 +1231,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C12" t="n">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="D12" t="n">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="D13" t="n">
-        <v>123</v>
+        <v>127</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C14" t="n">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="D14" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="15">
@@ -1273,13 +1273,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
     </row>
     <row r="16">
@@ -1287,13 +1287,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="17">
@@ -1304,10 +1304,10 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D17" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18">
@@ -1318,7 +1318,7 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D18" t="n">
         <v>39</v>
@@ -1335,7 +1335,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="20">
@@ -1349,7 +1349,7 @@
         <v>29</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="21">
@@ -1360,10 +1360,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="D21" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6624</v>
+        <v>10621</v>
       </c>
       <c r="C2" t="n">
-        <v>11539</v>
+        <v>7733</v>
       </c>
       <c r="D2" t="n">
-        <v>26123</v>
+        <v>36370</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3931</v>
+        <v>4606</v>
       </c>
       <c r="C3" t="n">
-        <v>9454</v>
+        <v>5815</v>
       </c>
       <c r="D3" t="n">
-        <v>16483</v>
+        <v>23179</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2725</v>
+        <v>2573</v>
       </c>
       <c r="C4" t="n">
-        <v>7803</v>
+        <v>5557</v>
       </c>
       <c r="D4" t="n">
-        <v>8487</v>
+        <v>12607</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2024</v>
+        <v>2009</v>
       </c>
       <c r="C5" t="n">
-        <v>6064</v>
+        <v>4098</v>
       </c>
       <c r="D5" t="n">
-        <v>3331</v>
+        <v>4939</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1407</v>
+        <v>1496</v>
       </c>
       <c r="C6" t="n">
-        <v>4837</v>
+        <v>2823</v>
       </c>
       <c r="D6" t="n">
-        <v>1333</v>
+        <v>1792</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>801</v>
+        <v>866</v>
       </c>
       <c r="C7" t="n">
-        <v>3837</v>
+        <v>1766</v>
       </c>
       <c r="D7" t="n">
-        <v>717</v>
+        <v>800</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>370</v>
+        <v>404</v>
       </c>
       <c r="C8" t="n">
-        <v>2630</v>
+        <v>1044</v>
       </c>
       <c r="D8" t="n">
-        <v>461</v>
+        <v>490</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>142</v>
+        <v>155</v>
       </c>
       <c r="C9" t="n">
-        <v>1373</v>
+        <v>564</v>
       </c>
       <c r="D9" t="n">
-        <v>324</v>
+        <v>335</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="C10" t="n">
-        <v>561</v>
+        <v>303</v>
       </c>
       <c r="D10" t="n">
-        <v>250</v>
+        <v>253</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="C11" t="n">
-        <v>237</v>
+        <v>202</v>
       </c>
       <c r="D11" t="n">
-        <v>200</v>
+        <v>211</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C12" t="n">
-        <v>149</v>
+        <v>156</v>
       </c>
       <c r="D12" t="n">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>111</v>
+        <v>119</v>
       </c>
       <c r="D13" t="n">
-        <v>124</v>
+        <v>129</v>
       </c>
     </row>
     <row r="14">
@@ -1570,10 +1570,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C14" t="n">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="D14" t="n">
         <v>100</v>
@@ -1584,13 +1584,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>83</v>
       </c>
     </row>
     <row r="16">
@@ -1598,13 +1598,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="17">
@@ -1612,13 +1612,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D17" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18">
@@ -1629,7 +1629,7 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D18" t="n">
         <v>39</v>
@@ -1643,10 +1643,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="20">
@@ -1660,7 +1660,7 @@
         <v>29</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="21">
@@ -1671,10 +1671,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="D21" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6277</v>
+        <v>9449</v>
       </c>
       <c r="C2" t="n">
-        <v>8308</v>
+        <v>5196</v>
       </c>
       <c r="D2" t="n">
-        <v>21847</v>
+        <v>29695</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4699</v>
+        <v>5174</v>
       </c>
       <c r="C3" t="n">
-        <v>13519</v>
+        <v>8759</v>
       </c>
       <c r="D3" t="n">
-        <v>17562</v>
+        <v>25404</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1870</v>
+        <v>1856</v>
       </c>
       <c r="C4" t="n">
-        <v>9791</v>
+        <v>7081</v>
       </c>
       <c r="D4" t="n">
-        <v>7793</v>
+        <v>11717</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1300</v>
+        <v>1382</v>
       </c>
       <c r="C5" t="n">
-        <v>4740</v>
+        <v>2766</v>
       </c>
       <c r="D5" t="n">
-        <v>2169</v>
+        <v>3131</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>740</v>
+        <v>800</v>
       </c>
       <c r="C6" t="n">
-        <v>3760</v>
+        <v>1730</v>
       </c>
       <c r="D6" t="n">
-        <v>702</v>
+        <v>784</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>341</v>
+        <v>373</v>
       </c>
       <c r="C7" t="n">
-        <v>2577</v>
+        <v>1023</v>
       </c>
       <c r="D7" t="n">
-        <v>451</v>
+        <v>480</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>131</v>
+        <v>143</v>
       </c>
       <c r="C8" t="n">
-        <v>1345</v>
+        <v>552</v>
       </c>
       <c r="D8" t="n">
-        <v>317</v>
+        <v>328</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="C9" t="n">
-        <v>549</v>
+        <v>296</v>
       </c>
       <c r="D9" t="n">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="C10" t="n">
-        <v>232</v>
+        <v>197</v>
       </c>
       <c r="D10" t="n">
-        <v>196</v>
+        <v>206</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C11" t="n">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="D11" t="n">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="D12" t="n">
-        <v>121</v>
+        <v>126</v>
       </c>
     </row>
     <row r="13">
@@ -1867,10 +1867,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C13" t="n">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="D13" t="n">
         <v>98</v>
@@ -1881,13 +1881,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="D14" t="n">
-        <v>78</v>
+        <v>81</v>
       </c>
     </row>
     <row r="15">
@@ -1895,13 +1895,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="D15" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="16">
@@ -1909,10 +1909,10 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C16" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D16" t="n">
         <v>49</v>
@@ -1926,7 +1926,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D17" t="n">
         <v>38</v>
@@ -1940,10 +1940,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D18" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="19">
@@ -1957,7 +1957,7 @@
         <v>28</v>
       </c>
       <c r="D19" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="20">
@@ -1968,10 +1968,10 @@
         <v>8</v>
       </c>
       <c r="C20" t="n">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="D20" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3910</v>
+        <v>5496</v>
       </c>
       <c r="C2" t="n">
-        <v>4005</v>
+        <v>2768</v>
       </c>
       <c r="D2" t="n">
-        <v>15534</v>
+        <v>20168</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4620</v>
+        <v>5964</v>
       </c>
       <c r="C3" t="n">
-        <v>10328</v>
+        <v>6449</v>
       </c>
       <c r="D3" t="n">
-        <v>17295</v>
+        <v>24524</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2483</v>
+        <v>2713</v>
       </c>
       <c r="C4" t="n">
-        <v>11573</v>
+        <v>7926</v>
       </c>
       <c r="D4" t="n">
-        <v>8943</v>
+        <v>13688</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1419</v>
+        <v>1509</v>
       </c>
       <c r="C5" t="n">
-        <v>6714</v>
+        <v>4663</v>
       </c>
       <c r="D5" t="n">
-        <v>2792</v>
+        <v>4167</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>860</v>
+        <v>955</v>
       </c>
       <c r="C6" t="n">
-        <v>4302</v>
+        <v>2203</v>
       </c>
       <c r="D6" t="n">
-        <v>840</v>
+        <v>1022</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>314</v>
+        <v>350</v>
       </c>
       <c r="C7" t="n">
-        <v>3056</v>
+        <v>1296</v>
       </c>
       <c r="D7" t="n">
-        <v>491</v>
+        <v>524</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>107</v>
+        <v>120</v>
       </c>
       <c r="C8" t="n">
-        <v>1725</v>
+        <v>720</v>
       </c>
       <c r="D8" t="n">
-        <v>326</v>
+        <v>342</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="C9" t="n">
-        <v>554</v>
+        <v>345</v>
       </c>
       <c r="D9" t="n">
-        <v>253</v>
+        <v>257</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C10" t="n">
-        <v>239</v>
+        <v>219</v>
       </c>
       <c r="D10" t="n">
-        <v>205</v>
+        <v>213</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>158</v>
+        <v>169</v>
       </c>
       <c r="D11" t="n">
-        <v>163</v>
+        <v>165</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>89</v>
+        <v>101</v>
       </c>
       <c r="D12" t="n">
-        <v>129</v>
+        <v>131</v>
       </c>
     </row>
     <row r="13">
@@ -2178,13 +2178,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="D13" t="n">
-        <v>96</v>
+        <v>100</v>
       </c>
     </row>
     <row r="14">
@@ -2192,13 +2192,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="D14" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="15">
@@ -2209,7 +2209,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D15" t="n">
         <v>48</v>
@@ -2223,7 +2223,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D16" t="n">
         <v>37</v>
@@ -2237,10 +2237,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D17" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="18">
@@ -2254,7 +2254,7 @@
         <v>27</v>
       </c>
       <c r="D18" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="19">
@@ -2265,10 +2265,10 @@
         <v>7</v>
       </c>
       <c r="C19" t="n">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="D19" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3873</v>
+        <v>5779</v>
       </c>
       <c r="C2" t="n">
-        <v>5528</v>
+        <v>8085</v>
       </c>
       <c r="D2" t="n">
-        <v>22892</v>
+        <v>21185</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3691</v>
+        <v>4837</v>
       </c>
       <c r="C3" t="n">
-        <v>6693</v>
+        <v>4145</v>
       </c>
       <c r="D3" t="n">
-        <v>15935</v>
+        <v>22444</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2849</v>
+        <v>3544</v>
       </c>
       <c r="C4" t="n">
-        <v>10869</v>
+        <v>7023</v>
       </c>
       <c r="D4" t="n">
-        <v>9954</v>
+        <v>14908</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1640</v>
+        <v>1793</v>
       </c>
       <c r="C5" t="n">
-        <v>8673</v>
+        <v>6177</v>
       </c>
       <c r="D5" t="n">
-        <v>3592</v>
+        <v>5594</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>988</v>
+        <v>1093</v>
       </c>
       <c r="C6" t="n">
-        <v>5258</v>
+        <v>3291</v>
       </c>
       <c r="D6" t="n">
-        <v>1091</v>
+        <v>1491</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>453</v>
+        <v>520</v>
       </c>
       <c r="C7" t="n">
-        <v>3585</v>
+        <v>1708</v>
       </c>
       <c r="D7" t="n">
-        <v>530</v>
+        <v>596</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>152</v>
+        <v>176</v>
       </c>
       <c r="C8" t="n">
-        <v>2236</v>
+        <v>963</v>
       </c>
       <c r="D8" t="n">
-        <v>342</v>
+        <v>361</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="C9" t="n">
-        <v>960</v>
+        <v>491</v>
       </c>
       <c r="D9" t="n">
-        <v>258</v>
+        <v>264</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C10" t="n">
-        <v>342</v>
+        <v>267</v>
       </c>
       <c r="D10" t="n">
-        <v>209</v>
+        <v>217</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="D11" t="n">
-        <v>166</v>
+        <v>169</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>106</v>
+        <v>122</v>
       </c>
       <c r="D12" t="n">
-        <v>130</v>
+        <v>133</v>
       </c>
     </row>
     <row r="13">
@@ -2489,13 +2489,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="D13" t="n">
-        <v>99</v>
+        <v>103</v>
       </c>
     </row>
     <row r="14">
@@ -2506,10 +2506,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="D14" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="15">
@@ -2520,10 +2520,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D15" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="16">
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D16" t="n">
         <v>36</v>
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D17" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="18">
@@ -2562,10 +2562,10 @@
         <v>6</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D18" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="19">
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="D19" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2378</v>
+        <v>3387</v>
       </c>
       <c r="C2" t="n">
-        <v>2776</v>
+        <v>3723</v>
       </c>
       <c r="D2" t="n">
-        <v>16124</v>
+        <v>14610</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3635</v>
+        <v>4931</v>
       </c>
       <c r="C3" t="n">
-        <v>6178</v>
+        <v>5367</v>
       </c>
       <c r="D3" t="n">
-        <v>16271</v>
+        <v>21764</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3090</v>
+        <v>3927</v>
       </c>
       <c r="C4" t="n">
-        <v>10483</v>
+        <v>6584</v>
       </c>
       <c r="D4" t="n">
-        <v>10657</v>
+        <v>15947</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1705</v>
+        <v>1880</v>
       </c>
       <c r="C5" t="n">
-        <v>10501</v>
+        <v>7286</v>
       </c>
       <c r="D5" t="n">
-        <v>3698</v>
+        <v>6049</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>792</v>
+        <v>934</v>
       </c>
       <c r="C6" t="n">
-        <v>6120</v>
+        <v>3955</v>
       </c>
       <c r="D6" t="n">
-        <v>1075</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>140</v>
+        <v>162</v>
       </c>
       <c r="C7" t="n">
-        <v>3826</v>
+        <v>1779</v>
       </c>
       <c r="D7" t="n">
-        <v>535</v>
+        <v>596</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="C8" t="n">
-        <v>1554</v>
+        <v>783</v>
       </c>
       <c r="D8" t="n">
-        <v>363</v>
+        <v>382</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C9" t="n">
-        <v>335</v>
+        <v>261</v>
       </c>
       <c r="D9" t="n">
-        <v>278</v>
+        <v>290</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="D10" t="n">
-        <v>162</v>
+        <v>165</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C11" t="n">
-        <v>103</v>
+        <v>119</v>
       </c>
       <c r="D11" t="n">
-        <v>127</v>
+        <v>130</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="D12" t="n">
-        <v>97</v>
+        <v>100</v>
       </c>
     </row>
     <row r="13">
@@ -2803,10 +2803,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="D13" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="14">
@@ -2817,10 +2817,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D14" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="15">
@@ -2831,7 +2831,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D15" t="n">
         <v>35</v>
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D16" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="17">
@@ -2859,10 +2859,10 @@
         <v>5</v>
       </c>
       <c r="C17" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D17" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="18">
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="D18" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3567</v>
+        <v>4010</v>
       </c>
       <c r="C2" t="n">
-        <v>3864</v>
+        <v>5163</v>
       </c>
       <c r="D2" t="n">
-        <v>13573</v>
+        <v>17511</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2705</v>
+        <v>3631</v>
       </c>
       <c r="C3" t="n">
-        <v>4246</v>
+        <v>4095</v>
       </c>
       <c r="D3" t="n">
-        <v>15341</v>
+        <v>19328</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2878</v>
+        <v>3821</v>
       </c>
       <c r="C4" t="n">
-        <v>8363</v>
+        <v>5926</v>
       </c>
       <c r="D4" t="n">
-        <v>11141</v>
+        <v>16411</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1987</v>
+        <v>2385</v>
       </c>
       <c r="C5" t="n">
-        <v>10375</v>
+        <v>6887</v>
       </c>
       <c r="D5" t="n">
-        <v>4520</v>
+        <v>7443</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1013</v>
+        <v>1185</v>
       </c>
       <c r="C6" t="n">
-        <v>7851</v>
+        <v>5364</v>
       </c>
       <c r="D6" t="n">
-        <v>1388</v>
+        <v>2040</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>280</v>
+        <v>349</v>
       </c>
       <c r="C7" t="n">
-        <v>4753</v>
+        <v>2687</v>
       </c>
       <c r="D7" t="n">
-        <v>598</v>
+        <v>703</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>62</v>
+        <v>76</v>
       </c>
       <c r="C8" t="n">
-        <v>2340</v>
+        <v>1159</v>
       </c>
       <c r="D8" t="n">
-        <v>379</v>
+        <v>404</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="C9" t="n">
-        <v>703</v>
+        <v>437</v>
       </c>
       <c r="D9" t="n">
-        <v>284</v>
+        <v>297</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>222</v>
+        <v>209</v>
       </c>
       <c r="D10" t="n">
-        <v>168</v>
+        <v>173</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>122</v>
+        <v>139</v>
       </c>
       <c r="D11" t="n">
-        <v>132</v>
+        <v>136</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="D12" t="n">
-        <v>97</v>
+        <v>101</v>
       </c>
     </row>
     <row r="13">
@@ -3114,10 +3114,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="D13" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D14" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D15" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="16">
@@ -3156,10 +3156,10 @@
         <v>4</v>
       </c>
       <c r="C16" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D16" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="D17" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="18">
@@ -3184,10 +3184,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2386</v>
+        <v>2798</v>
       </c>
       <c r="C2" t="n">
-        <v>2292</v>
+        <v>2860</v>
       </c>
       <c r="D2" t="n">
-        <v>10056</v>
+        <v>14924</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2595</v>
+        <v>3289</v>
       </c>
       <c r="C3" t="n">
-        <v>3753</v>
+        <v>4099</v>
       </c>
       <c r="D3" t="n">
-        <v>14332</v>
+        <v>18058</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2583</v>
+        <v>3465</v>
       </c>
       <c r="C4" t="n">
-        <v>6888</v>
+        <v>5217</v>
       </c>
       <c r="D4" t="n">
-        <v>11540</v>
+        <v>16461</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2142</v>
+        <v>2666</v>
       </c>
       <c r="C5" t="n">
-        <v>9801</v>
+        <v>6657</v>
       </c>
       <c r="D5" t="n">
-        <v>5061</v>
+        <v>8392</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1145</v>
+        <v>1396</v>
       </c>
       <c r="C6" t="n">
-        <v>8889</v>
+        <v>6058</v>
       </c>
       <c r="D6" t="n">
-        <v>1652</v>
+        <v>2522</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>249</v>
+        <v>325</v>
       </c>
       <c r="C7" t="n">
-        <v>5745</v>
+        <v>3526</v>
       </c>
       <c r="D7" t="n">
-        <v>655</v>
+        <v>813</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>49</v>
+        <v>62</v>
       </c>
       <c r="C8" t="n">
-        <v>2901</v>
+        <v>1517</v>
       </c>
       <c r="D8" t="n">
-        <v>384</v>
+        <v>417</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="C9" t="n">
-        <v>740</v>
+        <v>510</v>
       </c>
       <c r="D9" t="n">
-        <v>281</v>
+        <v>295</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C10" t="n">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="D10" t="n">
-        <v>172</v>
+        <v>177</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>119</v>
+        <v>137</v>
       </c>
       <c r="D11" t="n">
-        <v>133</v>
+        <v>138</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>71</v>
+        <v>83</v>
       </c>
       <c r="D12" t="n">
-        <v>89</v>
+        <v>93</v>
       </c>
     </row>
     <row r="13">
@@ -3425,10 +3425,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D13" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D14" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="15">
@@ -3453,10 +3453,10 @@
         <v>3</v>
       </c>
       <c r="C15" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D15" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="D16" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17">
@@ -3481,10 +3481,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3610</v>
+        <v>3968</v>
       </c>
       <c r="C2" t="n">
-        <v>6581</v>
+        <v>8660</v>
       </c>
       <c r="D2" t="n">
-        <v>17469</v>
+        <v>27764</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2130</v>
+        <v>2621</v>
       </c>
       <c r="C3" t="n">
-        <v>2877</v>
+        <v>3233</v>
       </c>
       <c r="D3" t="n">
-        <v>12958</v>
+        <v>16526</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2248</v>
+        <v>2957</v>
       </c>
       <c r="C4" t="n">
-        <v>5510</v>
+        <v>4586</v>
       </c>
       <c r="D4" t="n">
-        <v>11564</v>
+        <v>16190</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2107</v>
+        <v>2703</v>
       </c>
       <c r="C5" t="n">
-        <v>8506</v>
+        <v>5924</v>
       </c>
       <c r="D5" t="n">
-        <v>5715</v>
+        <v>9221</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1337</v>
+        <v>1679</v>
       </c>
       <c r="C6" t="n">
-        <v>9143</v>
+        <v>6301</v>
       </c>
       <c r="D6" t="n">
-        <v>2007</v>
+        <v>3197</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>452</v>
+        <v>599</v>
       </c>
       <c r="C7" t="n">
-        <v>6821</v>
+        <v>4467</v>
       </c>
       <c r="D7" t="n">
-        <v>765</v>
+        <v>1022</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>89</v>
+        <v>119</v>
       </c>
       <c r="C8" t="n">
-        <v>3848</v>
+        <v>2225</v>
       </c>
       <c r="D8" t="n">
-        <v>409</v>
+        <v>459</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="C9" t="n">
-        <v>1375</v>
+        <v>850</v>
       </c>
       <c r="D9" t="n">
-        <v>290</v>
+        <v>308</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C10" t="n">
-        <v>364</v>
+        <v>310</v>
       </c>
       <c r="D10" t="n">
-        <v>178</v>
+        <v>185</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>145</v>
+        <v>162</v>
       </c>
       <c r="D11" t="n">
-        <v>134</v>
+        <v>141</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>82</v>
+        <v>97</v>
       </c>
       <c r="D12" t="n">
-        <v>91</v>
+        <v>94</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="D13" t="n">
-        <v>62</v>
+        <v>65</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D14" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="15">
@@ -3764,10 +3764,10 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D15" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="D16" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7941</v>
+        <v>5059</v>
       </c>
       <c r="C2" t="n">
-        <v>19492</v>
+        <v>3893</v>
       </c>
       <c r="D2" t="n">
-        <v>3106</v>
+        <v>6750</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2664</v>
+        <v>2842</v>
       </c>
       <c r="C2" t="n">
-        <v>3949</v>
+        <v>4918</v>
       </c>
       <c r="D2" t="n">
-        <v>12996</v>
+        <v>20435</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2811</v>
+        <v>3514</v>
       </c>
       <c r="C3" t="n">
-        <v>3990</v>
+        <v>4771</v>
       </c>
       <c r="D3" t="n">
-        <v>14306</v>
+        <v>18729</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3096</v>
+        <v>4009</v>
       </c>
       <c r="C4" t="n">
-        <v>8316</v>
+        <v>6563</v>
       </c>
       <c r="D4" t="n">
-        <v>11639</v>
+        <v>16667</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1235</v>
+        <v>1626</v>
       </c>
       <c r="C5" t="n">
-        <v>12663</v>
+        <v>8807</v>
       </c>
       <c r="D5" t="n">
-        <v>5063</v>
+        <v>8205</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>417</v>
+        <v>553</v>
       </c>
       <c r="C6" t="n">
-        <v>8207</v>
+        <v>5612</v>
       </c>
       <c r="D6" t="n">
-        <v>1623</v>
+        <v>2437</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>82</v>
+        <v>109</v>
       </c>
       <c r="C7" t="n">
-        <v>3771</v>
+        <v>2180</v>
       </c>
       <c r="D7" t="n">
-        <v>490</v>
+        <v>580</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="C8" t="n">
-        <v>1347</v>
+        <v>833</v>
       </c>
       <c r="D8" t="n">
-        <v>284</v>
+        <v>301</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C9" t="n">
-        <v>356</v>
+        <v>303</v>
       </c>
       <c r="D9" t="n">
-        <v>174</v>
+        <v>181</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>142</v>
+        <v>158</v>
       </c>
       <c r="D10" t="n">
-        <v>131</v>
+        <v>138</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="D11" t="n">
-        <v>89</v>
+        <v>92</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="D12" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D13" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="14">
@@ -4372,10 +4372,10 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D14" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="D15" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16">
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7977</v>
+        <v>7567</v>
       </c>
       <c r="C2" t="n">
-        <v>12209</v>
+        <v>2948</v>
       </c>
       <c r="D2" t="n">
-        <v>17827</v>
+        <v>9685</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3372</v>
+        <v>2150</v>
       </c>
       <c r="C3" t="n">
-        <v>9823</v>
+        <v>1993</v>
       </c>
       <c r="D3" t="n">
-        <v>1161</v>
+        <v>1827</v>
       </c>
     </row>
     <row r="4">
@@ -4543,7 +4543,7 @@
         <v>79</v>
       </c>
       <c r="C4" t="n">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="D4" t="n">
         <v>1538</v>
@@ -4554,10 +4554,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C5" t="n">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="D5" t="n">
         <v>1161</v>
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="C6" t="n">
-        <v>454</v>
+        <v>459</v>
       </c>
       <c r="D6" t="n">
-        <v>816</v>
+        <v>808</v>
       </c>
     </row>
     <row r="7">
@@ -4588,7 +4588,7 @@
         <v>350</v>
       </c>
       <c r="D7" t="n">
-        <v>538</v>
+        <v>546</v>
       </c>
     </row>
     <row r="8">
@@ -4596,7 +4596,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C8" t="n">
         <v>260</v>
@@ -4610,7 +4610,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C9" t="n">
         <v>205</v>
@@ -4655,7 +4655,7 @@
         <v>26</v>
       </c>
       <c r="C12" t="n">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D12" t="n">
         <v>199</v>
@@ -4669,7 +4669,7 @@
         <v>19</v>
       </c>
       <c r="C13" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D13" t="n">
         <v>170</v>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5594</v>
+        <v>5646</v>
       </c>
       <c r="C2" t="n">
-        <v>5234</v>
+        <v>4732</v>
       </c>
       <c r="D2" t="n">
-        <v>15873</v>
+        <v>24685</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4627</v>
+        <v>4045</v>
       </c>
       <c r="C3" t="n">
-        <v>9730</v>
+        <v>2189</v>
       </c>
       <c r="D3" t="n">
-        <v>3743</v>
+        <v>3012</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1470</v>
+        <v>967</v>
       </c>
       <c r="C4" t="n">
-        <v>5704</v>
+        <v>1230</v>
       </c>
       <c r="D4" t="n">
-        <v>1404</v>
+        <v>1549</v>
       </c>
     </row>
     <row r="5">
@@ -4865,13 +4865,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C5" t="n">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="D5" t="n">
-        <v>1198</v>
+        <v>1186</v>
       </c>
     </row>
     <row r="6">
@@ -4882,10 +4882,10 @@
         <v>183</v>
       </c>
       <c r="C6" t="n">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="D6" t="n">
-        <v>859</v>
+        <v>864</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C7" t="n">
-        <v>405</v>
+        <v>409</v>
       </c>
       <c r="D7" t="n">
-        <v>584</v>
+        <v>589</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C8" t="n">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="D8" t="n">
-        <v>443</v>
+        <v>441</v>
       </c>
     </row>
     <row r="9">
@@ -4921,13 +4921,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C9" t="n">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="D9" t="n">
-        <v>359</v>
+        <v>363</v>
       </c>
     </row>
     <row r="10">
@@ -4935,7 +4935,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C10" t="n">
         <v>192</v>
@@ -4983,7 +4983,7 @@
         <v>103</v>
       </c>
       <c r="D13" t="n">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="14">
@@ -4994,10 +4994,10 @@
         <v>15</v>
       </c>
       <c r="C14" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D14" t="n">
-        <v>146</v>
+        <v>148</v>
       </c>
     </row>
     <row r="15">
@@ -5005,10 +5005,10 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D15" t="n">
         <v>120</v>
@@ -5025,7 +5025,7 @@
         <v>71</v>
       </c>
       <c r="D16" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="17">
@@ -5039,7 +5039,7 @@
         <v>68</v>
       </c>
       <c r="D17" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="18">
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5032</v>
+        <v>5837</v>
       </c>
       <c r="C2" t="n">
-        <v>3715</v>
+        <v>3833</v>
       </c>
       <c r="D2" t="n">
-        <v>18721</v>
+        <v>36275</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4198</v>
+        <v>4016</v>
       </c>
       <c r="C3" t="n">
-        <v>6403</v>
+        <v>3095</v>
       </c>
       <c r="D3" t="n">
-        <v>5323</v>
+        <v>6262</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2568</v>
+        <v>2117</v>
       </c>
       <c r="C4" t="n">
-        <v>7733</v>
+        <v>1735</v>
       </c>
       <c r="D4" t="n">
-        <v>1774</v>
+        <v>1767</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>640</v>
+        <v>457</v>
       </c>
       <c r="C5" t="n">
-        <v>3165</v>
+        <v>777</v>
       </c>
       <c r="D5" t="n">
-        <v>1199</v>
+        <v>1219</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="C6" t="n">
-        <v>309</v>
+        <v>303</v>
       </c>
       <c r="D6" t="n">
-        <v>897</v>
+        <v>910</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C7" t="n">
-        <v>403</v>
+        <v>409</v>
       </c>
       <c r="D7" t="n">
-        <v>626</v>
+        <v>625</v>
       </c>
     </row>
     <row r="8">
@@ -5221,10 +5221,10 @@
         <v>125</v>
       </c>
       <c r="C8" t="n">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="D8" t="n">
-        <v>457</v>
+        <v>462</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C9" t="n">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="D9" t="n">
-        <v>369</v>
+        <v>372</v>
       </c>
     </row>
     <row r="10">
@@ -5249,10 +5249,10 @@
         <v>66</v>
       </c>
       <c r="C10" t="n">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="D10" t="n">
-        <v>349</v>
+        <v>346</v>
       </c>
     </row>
     <row r="11">
@@ -5260,13 +5260,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C11" t="n">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="D11" t="n">
-        <v>276</v>
+        <v>280</v>
       </c>
     </row>
     <row r="12">
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C12" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D12" t="n">
-        <v>213</v>
+        <v>211</v>
       </c>
     </row>
     <row r="13">
@@ -5305,10 +5305,10 @@
         <v>15</v>
       </c>
       <c r="C14" t="n">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="D14" t="n">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C15" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D15" t="n">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="16">
@@ -5347,7 +5347,7 @@
         <v>11</v>
       </c>
       <c r="C17" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D17" t="n">
         <v>78</v>
@@ -5361,7 +5361,7 @@
         <v>10</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D18" t="n">
         <v>60</v>
@@ -5403,10 +5403,10 @@
         <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D21" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6105</v>
+        <v>5184</v>
       </c>
       <c r="C2" t="n">
-        <v>9769</v>
+        <v>3363</v>
       </c>
       <c r="D2" t="n">
-        <v>28241</v>
+        <v>39224</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3778</v>
+        <v>4008</v>
       </c>
       <c r="C3" t="n">
-        <v>4432</v>
+        <v>3025</v>
       </c>
       <c r="D3" t="n">
-        <v>6886</v>
+        <v>10383</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2834</v>
+        <v>2582</v>
       </c>
       <c r="C4" t="n">
-        <v>6882</v>
+        <v>2443</v>
       </c>
       <c r="D4" t="n">
-        <v>2316</v>
+        <v>2516</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1305</v>
+        <v>1066</v>
       </c>
       <c r="C5" t="n">
-        <v>5349</v>
+        <v>1266</v>
       </c>
       <c r="D5" t="n">
-        <v>1261</v>
+        <v>1281</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>329</v>
+        <v>262</v>
       </c>
       <c r="C6" t="n">
-        <v>1704</v>
+        <v>537</v>
       </c>
       <c r="D6" t="n">
-        <v>925</v>
+        <v>950</v>
       </c>
     </row>
     <row r="7">
@@ -5518,10 +5518,10 @@
         <v>145</v>
       </c>
       <c r="C7" t="n">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="D7" t="n">
-        <v>664</v>
+        <v>659</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C8" t="n">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="D8" t="n">
-        <v>474</v>
+        <v>484</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="C9" t="n">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="D9" t="n">
-        <v>379</v>
+        <v>378</v>
       </c>
     </row>
     <row r="10">
@@ -5560,10 +5560,10 @@
         <v>70</v>
       </c>
       <c r="C10" t="n">
-        <v>231</v>
+        <v>237</v>
       </c>
       <c r="D10" t="n">
-        <v>348</v>
+        <v>346</v>
       </c>
     </row>
     <row r="11">
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C11" t="n">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="D11" t="n">
-        <v>280</v>
+        <v>284</v>
       </c>
     </row>
     <row r="12">
@@ -5588,10 +5588,10 @@
         <v>33</v>
       </c>
       <c r="C12" t="n">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="D12" t="n">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="13">
@@ -5602,10 +5602,10 @@
         <v>22</v>
       </c>
       <c r="C13" t="n">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D13" t="n">
-        <v>174</v>
+        <v>176</v>
       </c>
     </row>
     <row r="14">
@@ -5616,7 +5616,7 @@
         <v>15</v>
       </c>
       <c r="C14" t="n">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D14" t="n">
         <v>149</v>
@@ -5630,10 +5630,10 @@
         <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="D15" t="n">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="16">
@@ -5647,7 +5647,7 @@
         <v>73</v>
       </c>
       <c r="D16" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="17">
@@ -5672,10 +5672,10 @@
         <v>9</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D18" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="19">
@@ -5714,10 +5714,10 @@
         <v>21</v>
       </c>
       <c r="C21" t="n">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6254</v>
+        <v>6252</v>
       </c>
       <c r="C2" t="n">
-        <v>9117</v>
+        <v>7142</v>
       </c>
       <c r="D2" t="n">
-        <v>33059</v>
+        <v>45757</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3522</v>
+        <v>3350</v>
       </c>
       <c r="C3" t="n">
-        <v>5746</v>
+        <v>2620</v>
       </c>
       <c r="D3" t="n">
-        <v>8912</v>
+        <v>13203</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2020</v>
+        <v>2058</v>
       </c>
       <c r="C4" t="n">
-        <v>4519</v>
+        <v>2271</v>
       </c>
       <c r="D4" t="n">
-        <v>2625</v>
+        <v>3364</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1070</v>
+        <v>946</v>
       </c>
       <c r="C5" t="n">
-        <v>4448</v>
+        <v>1372</v>
       </c>
       <c r="D5" t="n">
-        <v>1138</v>
+        <v>1189</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>371</v>
+        <v>314</v>
       </c>
       <c r="C6" t="n">
-        <v>2298</v>
+        <v>614</v>
       </c>
       <c r="D6" t="n">
-        <v>737</v>
+        <v>758</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="C7" t="n">
-        <v>628</v>
+        <v>285</v>
       </c>
       <c r="D7" t="n">
-        <v>518</v>
+        <v>520</v>
       </c>
     </row>
     <row r="8">
@@ -5843,10 +5843,10 @@
         <v>58</v>
       </c>
       <c r="C8" t="n">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="D8" t="n">
-        <v>357</v>
+        <v>364</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C9" t="n">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="D9" t="n">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C10" t="n">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="D10" t="n">
-        <v>238</v>
+        <v>237</v>
       </c>
     </row>
     <row r="11">
@@ -5885,10 +5885,10 @@
         <v>21</v>
       </c>
       <c r="C11" t="n">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="D11" t="n">
-        <v>190</v>
+        <v>193</v>
       </c>
     </row>
     <row r="12">
@@ -5896,10 +5896,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C12" t="n">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="D12" t="n">
         <v>149</v>
@@ -5910,13 +5910,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C13" t="n">
         <v>73</v>
       </c>
       <c r="D13" t="n">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="14">
@@ -5927,7 +5927,7 @@
         <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D14" t="n">
         <v>97</v>
@@ -5941,10 +5941,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D15" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16">
@@ -5983,7 +5983,7 @@
         <v>2</v>
       </c>
       <c r="C18" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D18" t="n">
         <v>38</v>
@@ -6000,7 +6000,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20">
@@ -6025,10 +6025,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D21" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5867</v>
+        <v>4933</v>
       </c>
       <c r="C2" t="n">
-        <v>10671</v>
+        <v>8692</v>
       </c>
       <c r="D2" t="n">
-        <v>28048</v>
+        <v>43011</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4052</v>
+        <v>4013</v>
       </c>
       <c r="C3" t="n">
-        <v>6600</v>
+        <v>4562</v>
       </c>
       <c r="D3" t="n">
-        <v>12398</v>
+        <v>17939</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2378</v>
+        <v>2382</v>
       </c>
       <c r="C4" t="n">
-        <v>5143</v>
+        <v>2438</v>
       </c>
       <c r="D4" t="n">
-        <v>3727</v>
+        <v>5339</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1367</v>
+        <v>1348</v>
       </c>
       <c r="C5" t="n">
-        <v>4395</v>
+        <v>1878</v>
       </c>
       <c r="D5" t="n">
-        <v>1388</v>
+        <v>1591</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>649</v>
+        <v>585</v>
       </c>
       <c r="C6" t="n">
-        <v>3447</v>
+        <v>1036</v>
       </c>
       <c r="D6" t="n">
-        <v>792</v>
+        <v>822</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>209</v>
+        <v>186</v>
       </c>
       <c r="C7" t="n">
-        <v>1527</v>
+        <v>475</v>
       </c>
       <c r="D7" t="n">
-        <v>553</v>
+        <v>561</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="C8" t="n">
-        <v>430</v>
+        <v>257</v>
       </c>
       <c r="D8" t="n">
-        <v>381</v>
+        <v>389</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C9" t="n">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="D9" t="n">
-        <v>278</v>
+        <v>281</v>
       </c>
     </row>
     <row r="10">
@@ -6179,10 +6179,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C10" t="n">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="D10" t="n">
         <v>240</v>
@@ -6193,13 +6193,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C11" t="n">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="D11" t="n">
-        <v>193</v>
+        <v>198</v>
       </c>
     </row>
     <row r="12">
@@ -6210,10 +6210,10 @@
         <v>15</v>
       </c>
       <c r="C12" t="n">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="D12" t="n">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="13">
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C13" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="D13" t="n">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="14">
@@ -6235,13 +6235,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D14" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="15">
@@ -6252,7 +6252,7 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D15" t="n">
         <v>79</v>
@@ -6283,7 +6283,7 @@
         <v>36</v>
       </c>
       <c r="D17" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18">
@@ -6297,7 +6297,7 @@
         <v>33</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19">
@@ -6311,7 +6311,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="20">
@@ -6325,7 +6325,7 @@
         <v>29</v>
       </c>
       <c r="D20" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="21">
@@ -6336,10 +6336,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5745</v>
+        <v>4289</v>
       </c>
       <c r="C2" t="n">
-        <v>12767</v>
+        <v>6095</v>
       </c>
       <c r="D2" t="n">
-        <v>34918</v>
+        <v>35673</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4023</v>
+        <v>3682</v>
       </c>
       <c r="C3" t="n">
-        <v>7568</v>
+        <v>5923</v>
       </c>
       <c r="D3" t="n">
-        <v>13903</v>
+        <v>20658</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2702</v>
+        <v>2764</v>
       </c>
       <c r="C4" t="n">
-        <v>5819</v>
+        <v>3610</v>
       </c>
       <c r="D4" t="n">
-        <v>5195</v>
+        <v>7544</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1631</v>
+        <v>1634</v>
       </c>
       <c r="C5" t="n">
-        <v>4691</v>
+        <v>2150</v>
       </c>
       <c r="D5" t="n">
-        <v>1736</v>
+        <v>2262</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>890</v>
+        <v>882</v>
       </c>
       <c r="C6" t="n">
-        <v>3849</v>
+        <v>1466</v>
       </c>
       <c r="D6" t="n">
-        <v>884</v>
+        <v>950</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>365</v>
+        <v>339</v>
       </c>
       <c r="C7" t="n">
-        <v>2486</v>
+        <v>777</v>
       </c>
       <c r="D7" t="n">
-        <v>581</v>
+        <v>595</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="C8" t="n">
-        <v>956</v>
+        <v>370</v>
       </c>
       <c r="D8" t="n">
-        <v>405</v>
+        <v>415</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C9" t="n">
-        <v>308</v>
+        <v>233</v>
       </c>
       <c r="D9" t="n">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C10" t="n">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="D10" t="n">
-        <v>240</v>
+        <v>244</v>
       </c>
     </row>
     <row r="11">
@@ -6504,13 +6504,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C11" t="n">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="D11" t="n">
-        <v>197</v>
+        <v>202</v>
       </c>
     </row>
     <row r="12">
@@ -6521,7 +6521,7 @@
         <v>16</v>
       </c>
       <c r="C12" t="n">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="D12" t="n">
         <v>155</v>
@@ -6532,13 +6532,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="D13" t="n">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="14">
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="D14" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="15">
@@ -6563,7 +6563,7 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="D15" t="n">
         <v>80</v>
@@ -6577,10 +6577,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="17">
@@ -6594,7 +6594,7 @@
         <v>37</v>
       </c>
       <c r="D17" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18">
@@ -6605,7 +6605,7 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D18" t="n">
         <v>39</v>
@@ -6622,7 +6622,7 @@
         <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="20">
@@ -6647,10 +6647,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_population_iteration_86_growth_param_0.5.xlsx
+++ b/output/yearly_population_iteration_86_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5993</v>
+        <v>1060</v>
       </c>
       <c r="C2" t="n">
-        <v>10233</v>
+        <v>2887</v>
       </c>
       <c r="D2" t="n">
-        <v>38585</v>
+        <v>15055</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3272</v>
+        <v>1570</v>
       </c>
       <c r="C3" t="n">
-        <v>5232</v>
+        <v>7338</v>
       </c>
       <c r="D3" t="n">
-        <v>21485</v>
+        <v>14144</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2738</v>
+        <v>862</v>
       </c>
       <c r="C4" t="n">
-        <v>4778</v>
+        <v>10886</v>
       </c>
       <c r="D4" t="n">
-        <v>9706</v>
+        <v>6146</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1920</v>
+        <v>363</v>
       </c>
       <c r="C5" t="n">
-        <v>2862</v>
+        <v>7582</v>
       </c>
       <c r="D5" t="n">
-        <v>3084</v>
+        <v>1941</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1121</v>
+        <v>159</v>
       </c>
       <c r="C6" t="n">
-        <v>1777</v>
+        <v>3258</v>
       </c>
       <c r="D6" t="n">
-        <v>1163</v>
+        <v>712</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>527</v>
+        <v>89</v>
       </c>
       <c r="C7" t="n">
-        <v>1121</v>
+        <v>1055</v>
       </c>
       <c r="D7" t="n">
-        <v>642</v>
+        <v>487</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>191</v>
+        <v>71</v>
       </c>
       <c r="C8" t="n">
-        <v>565</v>
+        <v>369</v>
       </c>
       <c r="D8" t="n">
-        <v>440</v>
+        <v>362</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>70</v>
+        <v>52</v>
       </c>
       <c r="C9" t="n">
-        <v>293</v>
+        <v>274</v>
       </c>
       <c r="D9" t="n">
-        <v>309</v>
+        <v>318</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="C10" t="n">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="D10" t="n">
-        <v>246</v>
+        <v>267</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="C11" t="n">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="D11" t="n">
-        <v>206</v>
+        <v>208</v>
       </c>
     </row>
     <row r="12">
@@ -920,13 +920,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>128</v>
+        <v>107</v>
       </c>
       <c r="D12" t="n">
-        <v>158</v>
+        <v>173</v>
       </c>
     </row>
     <row r="13">
@@ -934,13 +934,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C13" t="n">
-        <v>101</v>
+        <v>76</v>
       </c>
       <c r="D13" t="n">
-        <v>125</v>
+        <v>138</v>
       </c>
     </row>
     <row r="14">
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>78</v>
+        <v>64</v>
       </c>
       <c r="D14" t="n">
-        <v>99</v>
+        <v>89</v>
       </c>
     </row>
     <row r="15">
@@ -965,10 +965,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D15" t="n">
-        <v>81</v>
+        <v>70</v>
       </c>
     </row>
     <row r="16">
@@ -976,13 +976,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C16" t="n">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="D16" t="n">
-        <v>66</v>
+        <v>53</v>
       </c>
     </row>
     <row r="17">
@@ -990,13 +990,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C17" t="n">
+        <v>52</v>
+      </c>
+      <c r="D17" t="n">
         <v>38</v>
-      </c>
-      <c r="D17" t="n">
-        <v>51</v>
       </c>
     </row>
     <row r="18">
@@ -1004,13 +1004,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>21</v>
       </c>
     </row>
     <row r="19">
@@ -1018,13 +1018,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>139</v>
       </c>
       <c r="D19" t="n">
-        <v>28</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20">
@@ -1035,10 +1035,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8684</v>
+        <v>686</v>
       </c>
       <c r="C2" t="n">
-        <v>6486</v>
+        <v>7029</v>
       </c>
       <c r="D2" t="n">
-        <v>40186</v>
+        <v>12644</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3650</v>
+        <v>1130</v>
       </c>
       <c r="C3" t="n">
-        <v>6636</v>
+        <v>4487</v>
       </c>
       <c r="D3" t="n">
-        <v>22366</v>
+        <v>13302</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2575</v>
+        <v>1021</v>
       </c>
       <c r="C4" t="n">
-        <v>4855</v>
+        <v>8924</v>
       </c>
       <c r="D4" t="n">
-        <v>11240</v>
+        <v>7341</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2020</v>
+        <v>509</v>
       </c>
       <c r="C5" t="n">
-        <v>3722</v>
+        <v>9041</v>
       </c>
       <c r="D5" t="n">
-        <v>4070</v>
+        <v>2568</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1341</v>
+        <v>224</v>
       </c>
       <c r="C6" t="n">
-        <v>2241</v>
+        <v>5290</v>
       </c>
       <c r="D6" t="n">
-        <v>1431</v>
+        <v>891</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>710</v>
+        <v>107</v>
       </c>
       <c r="C7" t="n">
-        <v>1422</v>
+        <v>2058</v>
       </c>
       <c r="D7" t="n">
-        <v>717</v>
+        <v>515</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>293</v>
+        <v>73</v>
       </c>
       <c r="C8" t="n">
-        <v>804</v>
+        <v>661</v>
       </c>
       <c r="D8" t="n">
-        <v>460</v>
+        <v>379</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>105</v>
+        <v>55</v>
       </c>
       <c r="C9" t="n">
-        <v>410</v>
+        <v>316</v>
       </c>
       <c r="D9" t="n">
-        <v>325</v>
+        <v>319</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>46</v>
+        <v>28</v>
       </c>
       <c r="C10" t="n">
-        <v>244</v>
+        <v>234</v>
       </c>
       <c r="D10" t="n">
-        <v>249</v>
+        <v>272</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="C11" t="n">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="D11" t="n">
-        <v>209</v>
+        <v>213</v>
       </c>
     </row>
     <row r="12">
@@ -1231,13 +1231,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>143</v>
+        <v>128</v>
       </c>
       <c r="D12" t="n">
-        <v>160</v>
+        <v>175</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C13" t="n">
-        <v>109</v>
+        <v>85</v>
       </c>
       <c r="D13" t="n">
-        <v>127</v>
+        <v>141</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C14" t="n">
-        <v>86</v>
+        <v>69</v>
       </c>
       <c r="D14" t="n">
-        <v>100</v>
+        <v>91</v>
       </c>
     </row>
     <row r="15">
@@ -1276,10 +1276,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D15" t="n">
-        <v>82</v>
+        <v>70</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="D16" t="n">
-        <v>66</v>
+        <v>52</v>
       </c>
     </row>
     <row r="17">
@@ -1301,13 +1301,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>40</v>
+        <v>57</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>36</v>
       </c>
     </row>
     <row r="18">
@@ -1315,13 +1315,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="C18" t="n">
-        <v>35</v>
+        <v>96</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>17</v>
       </c>
     </row>
     <row r="19">
@@ -1332,10 +1332,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>74</v>
       </c>
       <c r="D19" t="n">
-        <v>28</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20">
@@ -1346,10 +1346,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>107</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>10621</v>
+        <v>379</v>
       </c>
       <c r="C2" t="n">
-        <v>7733</v>
+        <v>3141</v>
       </c>
       <c r="D2" t="n">
-        <v>36370</v>
+        <v>8747</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4606</v>
+        <v>978</v>
       </c>
       <c r="C3" t="n">
-        <v>5815</v>
+        <v>5244</v>
       </c>
       <c r="D3" t="n">
-        <v>23179</v>
+        <v>12909</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2573</v>
+        <v>1108</v>
       </c>
       <c r="C4" t="n">
-        <v>5557</v>
+        <v>8019</v>
       </c>
       <c r="D4" t="n">
-        <v>12607</v>
+        <v>8042</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2009</v>
+        <v>497</v>
       </c>
       <c r="C5" t="n">
-        <v>4098</v>
+        <v>10282</v>
       </c>
       <c r="D5" t="n">
-        <v>4939</v>
+        <v>2834</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1496</v>
+        <v>194</v>
       </c>
       <c r="C6" t="n">
-        <v>2823</v>
+        <v>6328</v>
       </c>
       <c r="D6" t="n">
-        <v>1792</v>
+        <v>906</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>866</v>
+        <v>67</v>
       </c>
       <c r="C7" t="n">
-        <v>1766</v>
+        <v>1845</v>
       </c>
       <c r="D7" t="n">
-        <v>800</v>
+        <v>543</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>404</v>
+        <v>50</v>
       </c>
       <c r="C8" t="n">
-        <v>1044</v>
+        <v>523</v>
       </c>
       <c r="D8" t="n">
-        <v>490</v>
+        <v>427</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>155</v>
+        <v>25</v>
       </c>
       <c r="C9" t="n">
-        <v>564</v>
+        <v>229</v>
       </c>
       <c r="D9" t="n">
-        <v>335</v>
+        <v>363</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>60</v>
+        <v>14</v>
       </c>
       <c r="C10" t="n">
-        <v>303</v>
+        <v>182</v>
       </c>
       <c r="D10" t="n">
-        <v>253</v>
+        <v>208</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>31</v>
+        <v>9</v>
       </c>
       <c r="C11" t="n">
-        <v>202</v>
+        <v>125</v>
       </c>
       <c r="D11" t="n">
-        <v>211</v>
+        <v>171</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>156</v>
+        <v>83</v>
       </c>
       <c r="D12" t="n">
-        <v>162</v>
+        <v>138</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="C13" t="n">
-        <v>119</v>
+        <v>67</v>
       </c>
       <c r="D13" t="n">
-        <v>129</v>
+        <v>89</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>93</v>
+        <v>62</v>
       </c>
       <c r="D14" t="n">
-        <v>100</v>
+        <v>68</v>
       </c>
     </row>
     <row r="15">
@@ -1584,13 +1584,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="D15" t="n">
-        <v>83</v>
+        <v>50</v>
       </c>
     </row>
     <row r="16">
@@ -1598,13 +1598,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C16" t="n">
         <v>55</v>
       </c>
       <c r="D16" t="n">
-        <v>66</v>
+        <v>35</v>
       </c>
     </row>
     <row r="17">
@@ -1612,13 +1612,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="C17" t="n">
-        <v>42</v>
+        <v>94</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>16</v>
       </c>
     </row>
     <row r="18">
@@ -1626,13 +1626,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>35</v>
+        <v>72</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -1643,10 +1643,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1657,10 +1657,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>113</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>9449</v>
+        <v>650</v>
       </c>
       <c r="C2" t="n">
-        <v>5196</v>
+        <v>9603</v>
       </c>
       <c r="D2" t="n">
-        <v>29695</v>
+        <v>14465</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5174</v>
+        <v>621</v>
       </c>
       <c r="C3" t="n">
-        <v>8759</v>
+        <v>3723</v>
       </c>
       <c r="D3" t="n">
-        <v>25404</v>
+        <v>11545</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1856</v>
+        <v>936</v>
       </c>
       <c r="C4" t="n">
-        <v>7081</v>
+        <v>6543</v>
       </c>
       <c r="D4" t="n">
-        <v>11717</v>
+        <v>8591</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1382</v>
+        <v>656</v>
       </c>
       <c r="C5" t="n">
-        <v>2766</v>
+        <v>9102</v>
       </c>
       <c r="D5" t="n">
-        <v>3131</v>
+        <v>3547</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>800</v>
+        <v>280</v>
       </c>
       <c r="C6" t="n">
-        <v>1730</v>
+        <v>8137</v>
       </c>
       <c r="D6" t="n">
-        <v>784</v>
+        <v>1180</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>373</v>
+        <v>97</v>
       </c>
       <c r="C7" t="n">
-        <v>1023</v>
+        <v>3725</v>
       </c>
       <c r="D7" t="n">
-        <v>480</v>
+        <v>583</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>143</v>
+        <v>53</v>
       </c>
       <c r="C8" t="n">
-        <v>552</v>
+        <v>1025</v>
       </c>
       <c r="D8" t="n">
-        <v>328</v>
+        <v>440</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>55</v>
+        <v>28</v>
       </c>
       <c r="C9" t="n">
-        <v>296</v>
+        <v>333</v>
       </c>
       <c r="D9" t="n">
-        <v>247</v>
+        <v>369</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="C10" t="n">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="D10" t="n">
-        <v>206</v>
+        <v>222</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="C11" t="n">
-        <v>152</v>
+        <v>143</v>
       </c>
       <c r="D11" t="n">
-        <v>158</v>
+        <v>177</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="C12" t="n">
-        <v>116</v>
+        <v>94</v>
       </c>
       <c r="D12" t="n">
-        <v>126</v>
+        <v>141</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C13" t="n">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="D13" t="n">
-        <v>98</v>
+        <v>89</v>
       </c>
     </row>
     <row r="14">
@@ -1881,13 +1881,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C14" t="n">
+        <v>69</v>
+      </c>
+      <c r="D14" t="n">
         <v>68</v>
-      </c>
-      <c r="D14" t="n">
-        <v>81</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>53</v>
+        <v>66</v>
       </c>
       <c r="D15" t="n">
-        <v>64</v>
+        <v>49</v>
       </c>
     </row>
     <row r="16">
@@ -1909,13 +1909,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>41</v>
+        <v>92</v>
       </c>
       <c r="D16" t="n">
-        <v>49</v>
+        <v>30</v>
       </c>
     </row>
     <row r="17">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>34</v>
+        <v>97</v>
       </c>
       <c r="D17" t="n">
-        <v>38</v>
+        <v>10</v>
       </c>
     </row>
     <row r="18">
@@ -1940,10 +1940,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>31</v>
+        <v>2</v>
       </c>
       <c r="D18" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1954,10 +1954,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1965,13 +1965,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>112</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5496</v>
+        <v>408</v>
       </c>
       <c r="C2" t="n">
-        <v>2768</v>
+        <v>4629</v>
       </c>
       <c r="D2" t="n">
-        <v>20168</v>
+        <v>11395</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5964</v>
+        <v>552</v>
       </c>
       <c r="C3" t="n">
-        <v>6449</v>
+        <v>5612</v>
       </c>
       <c r="D3" t="n">
-        <v>24524</v>
+        <v>11383</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2713</v>
+        <v>775</v>
       </c>
       <c r="C4" t="n">
-        <v>7926</v>
+        <v>5341</v>
       </c>
       <c r="D4" t="n">
-        <v>13688</v>
+        <v>8809</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1509</v>
+        <v>712</v>
       </c>
       <c r="C5" t="n">
-        <v>4663</v>
+        <v>8279</v>
       </c>
       <c r="D5" t="n">
-        <v>4167</v>
+        <v>4088</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>955</v>
+        <v>344</v>
       </c>
       <c r="C6" t="n">
-        <v>2203</v>
+        <v>8871</v>
       </c>
       <c r="D6" t="n">
-        <v>1022</v>
+        <v>1393</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>350</v>
+        <v>101</v>
       </c>
       <c r="C7" t="n">
-        <v>1296</v>
+        <v>5103</v>
       </c>
       <c r="D7" t="n">
-        <v>524</v>
+        <v>637</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>120</v>
+        <v>49</v>
       </c>
       <c r="C8" t="n">
-        <v>720</v>
+        <v>1574</v>
       </c>
       <c r="D8" t="n">
-        <v>342</v>
+        <v>466</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>45</v>
+        <v>24</v>
       </c>
       <c r="C9" t="n">
-        <v>345</v>
+        <v>418</v>
       </c>
       <c r="D9" t="n">
-        <v>257</v>
+        <v>368</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="D10" t="n">
-        <v>213</v>
+        <v>228</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>169</v>
+        <v>147</v>
       </c>
       <c r="D11" t="n">
-        <v>165</v>
+        <v>183</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C12" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D12" t="n">
-        <v>131</v>
+        <v>133</v>
       </c>
     </row>
     <row r="13">
@@ -2178,13 +2178,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D13" t="n">
-        <v>100</v>
+        <v>92</v>
       </c>
     </row>
     <row r="14">
@@ -2195,10 +2195,10 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>51</v>
+        <v>64</v>
       </c>
       <c r="D14" t="n">
-        <v>62</v>
+        <v>54</v>
       </c>
     </row>
     <row r="15">
@@ -2206,13 +2206,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="C15" t="n">
-        <v>40</v>
+        <v>90</v>
       </c>
       <c r="D15" t="n">
-        <v>48</v>
+        <v>29</v>
       </c>
     </row>
     <row r="16">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>33</v>
+        <v>95</v>
       </c>
       <c r="D16" t="n">
-        <v>37</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17">
@@ -2237,10 +2237,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2262,13 +2262,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>109</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5779</v>
+        <v>541</v>
       </c>
       <c r="C2" t="n">
-        <v>8085</v>
+        <v>13730</v>
       </c>
       <c r="D2" t="n">
-        <v>21185</v>
+        <v>11983</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4837</v>
+        <v>418</v>
       </c>
       <c r="C3" t="n">
-        <v>4145</v>
+        <v>4649</v>
       </c>
       <c r="D3" t="n">
-        <v>22444</v>
+        <v>10637</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3544</v>
+        <v>607</v>
       </c>
       <c r="C4" t="n">
-        <v>7023</v>
+        <v>5349</v>
       </c>
       <c r="D4" t="n">
-        <v>14908</v>
+        <v>8936</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1793</v>
+        <v>671</v>
       </c>
       <c r="C5" t="n">
-        <v>6177</v>
+        <v>6865</v>
       </c>
       <c r="D5" t="n">
-        <v>5594</v>
+        <v>4643</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1093</v>
+        <v>439</v>
       </c>
       <c r="C6" t="n">
-        <v>3291</v>
+        <v>8554</v>
       </c>
       <c r="D6" t="n">
-        <v>1491</v>
+        <v>1737</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>520</v>
+        <v>164</v>
       </c>
       <c r="C7" t="n">
-        <v>1708</v>
+        <v>6628</v>
       </c>
       <c r="D7" t="n">
-        <v>596</v>
+        <v>726</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>176</v>
+        <v>59</v>
       </c>
       <c r="C8" t="n">
-        <v>963</v>
+        <v>2868</v>
       </c>
       <c r="D8" t="n">
-        <v>361</v>
+        <v>481</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>60</v>
+        <v>28</v>
       </c>
       <c r="C9" t="n">
-        <v>491</v>
+        <v>807</v>
       </c>
       <c r="D9" t="n">
-        <v>264</v>
+        <v>374</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="C10" t="n">
-        <v>267</v>
+        <v>279</v>
       </c>
       <c r="D10" t="n">
-        <v>217</v>
+        <v>241</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>187</v>
+        <v>168</v>
       </c>
       <c r="D11" t="n">
-        <v>169</v>
+        <v>184</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C12" t="n">
-        <v>122</v>
+        <v>114</v>
       </c>
       <c r="D12" t="n">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D13" t="n">
-        <v>103</v>
+        <v>93</v>
       </c>
     </row>
     <row r="14">
@@ -2503,13 +2503,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="D14" t="n">
-        <v>63</v>
+        <v>56</v>
       </c>
     </row>
     <row r="15">
@@ -2517,13 +2517,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="C15" t="n">
-        <v>45</v>
+        <v>94</v>
       </c>
       <c r="D15" t="n">
-        <v>48</v>
+        <v>28</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>36</v>
+        <v>93</v>
       </c>
       <c r="D16" t="n">
-        <v>36</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17">
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2559,13 +2559,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>66</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>59</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3387</v>
+        <v>380</v>
       </c>
       <c r="C2" t="n">
-        <v>3723</v>
+        <v>7688</v>
       </c>
       <c r="D2" t="n">
-        <v>14610</v>
+        <v>8819</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4931</v>
+        <v>594</v>
       </c>
       <c r="C3" t="n">
-        <v>5367</v>
+        <v>7222</v>
       </c>
       <c r="D3" t="n">
-        <v>21764</v>
+        <v>11493</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3927</v>
+        <v>926</v>
       </c>
       <c r="C4" t="n">
-        <v>6584</v>
+        <v>7713</v>
       </c>
       <c r="D4" t="n">
-        <v>15947</v>
+        <v>9133</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1880</v>
+        <v>430</v>
       </c>
       <c r="C5" t="n">
-        <v>7286</v>
+        <v>11169</v>
       </c>
       <c r="D5" t="n">
-        <v>6049</v>
+        <v>4238</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>934</v>
+        <v>151</v>
       </c>
       <c r="C6" t="n">
-        <v>3955</v>
+        <v>8255</v>
       </c>
       <c r="D6" t="n">
-        <v>1440</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>162</v>
+        <v>54</v>
       </c>
       <c r="C7" t="n">
-        <v>1779</v>
+        <v>2810</v>
       </c>
       <c r="D7" t="n">
-        <v>596</v>
+        <v>570</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>55</v>
+        <v>25</v>
       </c>
       <c r="C8" t="n">
-        <v>783</v>
+        <v>790</v>
       </c>
       <c r="D8" t="n">
-        <v>382</v>
+        <v>366</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="C9" t="n">
-        <v>261</v>
+        <v>273</v>
       </c>
       <c r="D9" t="n">
-        <v>290</v>
+        <v>236</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="C10" t="n">
-        <v>183</v>
+        <v>164</v>
       </c>
       <c r="D10" t="n">
-        <v>165</v>
+        <v>180</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C11" t="n">
-        <v>119</v>
+        <v>111</v>
       </c>
       <c r="D11" t="n">
-        <v>130</v>
+        <v>133</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D12" t="n">
-        <v>100</v>
+        <v>91</v>
       </c>
     </row>
     <row r="13">
@@ -2800,13 +2800,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>53</v>
+        <v>64</v>
       </c>
       <c r="D13" t="n">
-        <v>61</v>
+        <v>54</v>
       </c>
     </row>
     <row r="14">
@@ -2814,13 +2814,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>44</v>
+        <v>92</v>
       </c>
       <c r="D14" t="n">
-        <v>47</v>
+        <v>27</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>35</v>
+        <v>91</v>
       </c>
       <c r="D15" t="n">
-        <v>35</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16">
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -2856,13 +2856,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4010</v>
+        <v>218</v>
       </c>
       <c r="C2" t="n">
-        <v>5163</v>
+        <v>3461</v>
       </c>
       <c r="D2" t="n">
-        <v>17511</v>
+        <v>7395</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3631</v>
+        <v>430</v>
       </c>
       <c r="C3" t="n">
-        <v>4095</v>
+        <v>6579</v>
       </c>
       <c r="D3" t="n">
-        <v>19328</v>
+        <v>10322</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3821</v>
+        <v>647</v>
       </c>
       <c r="C4" t="n">
-        <v>5926</v>
+        <v>7081</v>
       </c>
       <c r="D4" t="n">
-        <v>16411</v>
+        <v>8854</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2385</v>
+        <v>433</v>
       </c>
       <c r="C5" t="n">
-        <v>6887</v>
+        <v>8452</v>
       </c>
       <c r="D5" t="n">
-        <v>7443</v>
+        <v>4407</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1185</v>
+        <v>145</v>
       </c>
       <c r="C6" t="n">
-        <v>5364</v>
+        <v>7819</v>
       </c>
       <c r="D6" t="n">
-        <v>2040</v>
+        <v>1533</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>349</v>
+        <v>40</v>
       </c>
       <c r="C7" t="n">
-        <v>2687</v>
+        <v>3569</v>
       </c>
       <c r="D7" t="n">
-        <v>703</v>
+        <v>540</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>76</v>
+        <v>12</v>
       </c>
       <c r="C8" t="n">
-        <v>1159</v>
+        <v>951</v>
       </c>
       <c r="D8" t="n">
-        <v>404</v>
+        <v>312</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>23</v>
+        <v>3</v>
       </c>
       <c r="C9" t="n">
-        <v>437</v>
+        <v>264</v>
       </c>
       <c r="D9" t="n">
-        <v>297</v>
+        <v>186</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>209</v>
+        <v>114</v>
       </c>
       <c r="D10" t="n">
-        <v>173</v>
+        <v>137</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>139</v>
+        <v>72</v>
       </c>
       <c r="D11" t="n">
-        <v>136</v>
+        <v>97</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>85</v>
+        <v>52</v>
       </c>
       <c r="D12" t="n">
-        <v>101</v>
+        <v>61</v>
       </c>
     </row>
     <row r="13">
@@ -3111,13 +3111,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="D13" t="n">
-        <v>61</v>
+        <v>31</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="D14" t="n">
-        <v>47</v>
+        <v>8</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3153,13 +3153,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>59</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>74</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3184,10 +3184,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2798</v>
+        <v>232</v>
       </c>
       <c r="C2" t="n">
-        <v>2860</v>
+        <v>5753</v>
       </c>
       <c r="D2" t="n">
-        <v>14924</v>
+        <v>10418</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3289</v>
+        <v>281</v>
       </c>
       <c r="C3" t="n">
-        <v>4099</v>
+        <v>4364</v>
       </c>
       <c r="D3" t="n">
-        <v>18058</v>
+        <v>9150</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3465</v>
+        <v>484</v>
       </c>
       <c r="C4" t="n">
-        <v>5217</v>
+        <v>6668</v>
       </c>
       <c r="D4" t="n">
-        <v>16461</v>
+        <v>8852</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2666</v>
+        <v>471</v>
       </c>
       <c r="C5" t="n">
-        <v>6657</v>
+        <v>7659</v>
       </c>
       <c r="D5" t="n">
-        <v>8392</v>
+        <v>5041</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1396</v>
+        <v>244</v>
       </c>
       <c r="C6" t="n">
-        <v>6058</v>
+        <v>8041</v>
       </c>
       <c r="D6" t="n">
-        <v>2522</v>
+        <v>1981</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>325</v>
+        <v>73</v>
       </c>
       <c r="C7" t="n">
-        <v>3526</v>
+        <v>5601</v>
       </c>
       <c r="D7" t="n">
-        <v>813</v>
+        <v>690</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>62</v>
+        <v>20</v>
       </c>
       <c r="C8" t="n">
-        <v>1517</v>
+        <v>2114</v>
       </c>
       <c r="D8" t="n">
-        <v>417</v>
+        <v>342</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="C9" t="n">
-        <v>510</v>
+        <v>549</v>
       </c>
       <c r="D9" t="n">
-        <v>295</v>
+        <v>203</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>221</v>
+        <v>172</v>
       </c>
       <c r="D10" t="n">
-        <v>177</v>
+        <v>141</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>137</v>
+        <v>88</v>
       </c>
       <c r="D11" t="n">
-        <v>138</v>
+        <v>101</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>83</v>
+        <v>59</v>
       </c>
       <c r="D12" t="n">
-        <v>93</v>
+        <v>63</v>
       </c>
     </row>
     <row r="13">
@@ -3422,13 +3422,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="D13" t="n">
-        <v>63</v>
+        <v>33</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>37</v>
+        <v>53</v>
       </c>
       <c r="D14" t="n">
-        <v>37</v>
+        <v>9</v>
       </c>
     </row>
     <row r="15">
@@ -3450,13 +3450,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>57</v>
+        <v>8</v>
       </c>
       <c r="D15" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>72</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3481,10 +3481,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3968</v>
+        <v>77</v>
       </c>
       <c r="C2" t="n">
-        <v>8660</v>
+        <v>6739</v>
       </c>
       <c r="D2" t="n">
-        <v>27764</v>
+        <v>11679</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2621</v>
+        <v>217</v>
       </c>
       <c r="C3" t="n">
-        <v>3233</v>
+        <v>4395</v>
       </c>
       <c r="D3" t="n">
-        <v>16526</v>
+        <v>8707</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2957</v>
+        <v>345</v>
       </c>
       <c r="C4" t="n">
-        <v>4586</v>
+        <v>5423</v>
       </c>
       <c r="D4" t="n">
-        <v>16190</v>
+        <v>8631</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2703</v>
+        <v>434</v>
       </c>
       <c r="C5" t="n">
-        <v>5924</v>
+        <v>7043</v>
       </c>
       <c r="D5" t="n">
-        <v>9221</v>
+        <v>5424</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1679</v>
+        <v>309</v>
       </c>
       <c r="C6" t="n">
-        <v>6301</v>
+        <v>7795</v>
       </c>
       <c r="D6" t="n">
-        <v>3197</v>
+        <v>2424</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>599</v>
+        <v>125</v>
       </c>
       <c r="C7" t="n">
-        <v>4467</v>
+        <v>6595</v>
       </c>
       <c r="D7" t="n">
-        <v>1022</v>
+        <v>872</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>119</v>
+        <v>35</v>
       </c>
       <c r="C8" t="n">
-        <v>2225</v>
+        <v>3582</v>
       </c>
       <c r="D8" t="n">
-        <v>459</v>
+        <v>382</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="C9" t="n">
-        <v>850</v>
+        <v>1177</v>
       </c>
       <c r="D9" t="n">
-        <v>308</v>
+        <v>220</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C10" t="n">
-        <v>310</v>
+        <v>316</v>
       </c>
       <c r="D10" t="n">
-        <v>185</v>
+        <v>147</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>162</v>
+        <v>118</v>
       </c>
       <c r="D11" t="n">
-        <v>141</v>
+        <v>103</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>97</v>
+        <v>68</v>
       </c>
       <c r="D12" t="n">
-        <v>94</v>
+        <v>66</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="D13" t="n">
-        <v>65</v>
+        <v>35</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="D14" t="n">
-        <v>38</v>
+        <v>11</v>
       </c>
     </row>
     <row r="15">
@@ -3761,13 +3761,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>59</v>
+        <v>20</v>
       </c>
       <c r="D15" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>2</v>
       </c>
       <c r="D16" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5059</v>
+        <v>1561</v>
       </c>
       <c r="C2" t="n">
-        <v>3893</v>
+        <v>22365</v>
       </c>
       <c r="D2" t="n">
-        <v>6750</v>
+        <v>9359</v>
       </c>
     </row>
     <row r="3">
@@ -3904,13 +3904,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>843</v>
+        <v>855</v>
       </c>
     </row>
     <row r="4">
@@ -3918,13 +3918,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>175</v>
+        <v>205</v>
       </c>
       <c r="C4" t="n">
-        <v>313</v>
+        <v>344</v>
       </c>
       <c r="D4" t="n">
-        <v>1805</v>
+        <v>1906</v>
       </c>
     </row>
     <row r="5">
@@ -3932,13 +3932,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>249</v>
+        <v>314</v>
       </c>
       <c r="C5" t="n">
-        <v>515</v>
+        <v>586</v>
       </c>
       <c r="D5" t="n">
-        <v>1038</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="6">
@@ -3946,13 +3946,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>182</v>
+        <v>255</v>
       </c>
       <c r="C6" t="n">
-        <v>395</v>
+        <v>488</v>
       </c>
       <c r="D6" t="n">
-        <v>777</v>
+        <v>898</v>
       </c>
     </row>
     <row r="7">
@@ -3960,13 +3960,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>129</v>
+        <v>202</v>
       </c>
       <c r="C7" t="n">
-        <v>293</v>
+        <v>388</v>
       </c>
       <c r="D7" t="n">
-        <v>496</v>
+        <v>596</v>
       </c>
     </row>
     <row r="8">
@@ -3974,13 +3974,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>99</v>
+        <v>171</v>
       </c>
       <c r="C8" t="n">
-        <v>222</v>
+        <v>307</v>
       </c>
       <c r="D8" t="n">
-        <v>420</v>
+        <v>531</v>
       </c>
     </row>
     <row r="9">
@@ -3988,13 +3988,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>75</v>
+        <v>136</v>
       </c>
       <c r="C9" t="n">
-        <v>187</v>
+        <v>277</v>
       </c>
       <c r="D9" t="n">
-        <v>349</v>
+        <v>445</v>
       </c>
     </row>
     <row r="10">
@@ -4002,13 +4002,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>53</v>
+        <v>105</v>
       </c>
       <c r="C10" t="n">
-        <v>173</v>
+        <v>265</v>
       </c>
       <c r="D10" t="n">
-        <v>362</v>
+        <v>485</v>
       </c>
     </row>
     <row r="11">
@@ -4016,13 +4016,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>34</v>
+        <v>71</v>
       </c>
       <c r="C11" t="n">
-        <v>137</v>
+        <v>215</v>
       </c>
       <c r="D11" t="n">
-        <v>245</v>
+        <v>327</v>
       </c>
     </row>
     <row r="12">
@@ -4030,13 +4030,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="C12" t="n">
-        <v>104</v>
+        <v>169</v>
       </c>
       <c r="D12" t="n">
-        <v>196</v>
+        <v>274</v>
       </c>
     </row>
     <row r="13">
@@ -4044,13 +4044,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="C13" t="n">
-        <v>84</v>
+        <v>142</v>
       </c>
       <c r="D13" t="n">
-        <v>168</v>
+        <v>234</v>
       </c>
     </row>
     <row r="14">
@@ -4058,13 +4058,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="C14" t="n">
-        <v>75</v>
+        <v>128</v>
       </c>
       <c r="D14" t="n">
-        <v>145</v>
+        <v>207</v>
       </c>
     </row>
     <row r="15">
@@ -4072,13 +4072,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="C15" t="n">
-        <v>72</v>
+        <v>127</v>
       </c>
       <c r="D15" t="n">
-        <v>117</v>
+        <v>171</v>
       </c>
     </row>
     <row r="16">
@@ -4086,13 +4086,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>124</v>
       </c>
       <c r="D16" t="n">
-        <v>97</v>
+        <v>140</v>
       </c>
     </row>
     <row r="17">
@@ -4100,13 +4100,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="C17" t="n">
-        <v>66</v>
+        <v>119</v>
       </c>
       <c r="D17" t="n">
-        <v>76</v>
+        <v>114</v>
       </c>
     </row>
     <row r="18">
@@ -4114,13 +4114,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="C18" t="n">
-        <v>63</v>
+        <v>116</v>
       </c>
       <c r="D18" t="n">
-        <v>57</v>
+        <v>85</v>
       </c>
     </row>
     <row r="19">
@@ -4128,13 +4128,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="C19" t="n">
-        <v>60</v>
+        <v>111</v>
       </c>
       <c r="D19" t="n">
-        <v>38</v>
+        <v>58</v>
       </c>
     </row>
     <row r="20">
@@ -4142,13 +4142,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>109</v>
       </c>
       <c r="D20" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
     </row>
     <row r="21">
@@ -4156,10 +4156,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="C21" t="n">
-        <v>72</v>
+        <v>131</v>
       </c>
       <c r="D21" t="n">
         <v>1</v>
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2842</v>
+        <v>87</v>
       </c>
       <c r="C2" t="n">
-        <v>4918</v>
+        <v>20568</v>
       </c>
       <c r="D2" t="n">
-        <v>20435</v>
+        <v>9877</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3514</v>
+        <v>139</v>
       </c>
       <c r="C3" t="n">
-        <v>4771</v>
+        <v>4746</v>
       </c>
       <c r="D3" t="n">
-        <v>18729</v>
+        <v>8506</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>4009</v>
+        <v>256</v>
       </c>
       <c r="C4" t="n">
-        <v>6563</v>
+        <v>4866</v>
       </c>
       <c r="D4" t="n">
-        <v>16667</v>
+        <v>8296</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1626</v>
+        <v>370</v>
       </c>
       <c r="C5" t="n">
-        <v>8807</v>
+        <v>6160</v>
       </c>
       <c r="D5" t="n">
-        <v>8205</v>
+        <v>5720</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>553</v>
+        <v>327</v>
       </c>
       <c r="C6" t="n">
-        <v>5612</v>
+        <v>7423</v>
       </c>
       <c r="D6" t="n">
-        <v>2437</v>
+        <v>2771</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>109</v>
+        <v>172</v>
       </c>
       <c r="C7" t="n">
-        <v>2180</v>
+        <v>6998</v>
       </c>
       <c r="D7" t="n">
-        <v>580</v>
+        <v>1076</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>23</v>
+        <v>59</v>
       </c>
       <c r="C8" t="n">
-        <v>833</v>
+        <v>4732</v>
       </c>
       <c r="D8" t="n">
-        <v>301</v>
+        <v>436</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="C9" t="n">
-        <v>303</v>
+        <v>2048</v>
       </c>
       <c r="D9" t="n">
-        <v>181</v>
+        <v>238</v>
       </c>
     </row>
     <row r="10">
@@ -4313,13 +4313,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C10" t="n">
-        <v>158</v>
+        <v>608</v>
       </c>
       <c r="D10" t="n">
-        <v>138</v>
+        <v>154</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>95</v>
+        <v>183</v>
       </c>
       <c r="D11" t="n">
-        <v>92</v>
+        <v>105</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>51</v>
+        <v>82</v>
       </c>
       <c r="D12" t="n">
-        <v>63</v>
+        <v>69</v>
       </c>
     </row>
     <row r="13">
@@ -4358,7 +4358,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>38</v>
+        <v>59</v>
       </c>
       <c r="D13" t="n">
         <v>37</v>
@@ -4369,13 +4369,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="D14" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>68</v>
+        <v>29</v>
       </c>
       <c r="D15" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -4400,7 +4400,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7567</v>
+        <v>2811</v>
       </c>
       <c r="C2" t="n">
-        <v>2948</v>
+        <v>13927</v>
       </c>
       <c r="D2" t="n">
-        <v>9685</v>
+        <v>21230</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2150</v>
+        <v>507</v>
       </c>
       <c r="C3" t="n">
-        <v>1993</v>
+        <v>8832</v>
       </c>
       <c r="D3" t="n">
-        <v>1827</v>
+        <v>1896</v>
       </c>
     </row>
     <row r="4">
@@ -4540,13 +4540,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="C4" t="n">
-        <v>114</v>
+        <v>134</v>
       </c>
       <c r="D4" t="n">
-        <v>1538</v>
+        <v>1446</v>
       </c>
     </row>
     <row r="5">
@@ -4554,13 +4554,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>191</v>
+        <v>148</v>
       </c>
       <c r="C5" t="n">
-        <v>384</v>
+        <v>338</v>
       </c>
       <c r="D5" t="n">
-        <v>1161</v>
+        <v>986</v>
       </c>
     </row>
     <row r="6">
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>202</v>
+        <v>143</v>
       </c>
       <c r="C6" t="n">
-        <v>459</v>
+        <v>356</v>
       </c>
       <c r="D6" t="n">
-        <v>808</v>
+        <v>712</v>
       </c>
     </row>
     <row r="7">
@@ -4582,13 +4582,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>145</v>
+        <v>102</v>
       </c>
       <c r="C7" t="n">
-        <v>350</v>
+        <v>277</v>
       </c>
       <c r="D7" t="n">
-        <v>546</v>
+        <v>466</v>
       </c>
     </row>
     <row r="8">
@@ -4596,13 +4596,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>105</v>
+        <v>78</v>
       </c>
       <c r="C8" t="n">
-        <v>260</v>
+        <v>206</v>
       </c>
       <c r="D8" t="n">
-        <v>429</v>
+        <v>384</v>
       </c>
     </row>
     <row r="9">
@@ -4610,13 +4610,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="C9" t="n">
-        <v>205</v>
+        <v>169</v>
       </c>
       <c r="D9" t="n">
-        <v>354</v>
+        <v>313</v>
       </c>
     </row>
     <row r="10">
@@ -4624,13 +4624,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>58</v>
+        <v>45</v>
       </c>
       <c r="C10" t="n">
-        <v>180</v>
+        <v>153</v>
       </c>
       <c r="D10" t="n">
-        <v>356</v>
+        <v>324</v>
       </c>
     </row>
     <row r="11">
@@ -4638,13 +4638,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="C11" t="n">
-        <v>154</v>
+        <v>128</v>
       </c>
       <c r="D11" t="n">
-        <v>261</v>
+        <v>231</v>
       </c>
     </row>
     <row r="12">
@@ -4652,13 +4652,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="C12" t="n">
-        <v>118</v>
+        <v>100</v>
       </c>
       <c r="D12" t="n">
-        <v>199</v>
+        <v>182</v>
       </c>
     </row>
     <row r="13">
@@ -4666,13 +4666,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C13" t="n">
-        <v>93</v>
+        <v>79</v>
       </c>
       <c r="D13" t="n">
-        <v>170</v>
+        <v>154</v>
       </c>
     </row>
     <row r="14">
@@ -4680,13 +4680,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="D14" t="n">
-        <v>146</v>
+        <v>133</v>
       </c>
     </row>
     <row r="15">
@@ -4694,13 +4694,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="D15" t="n">
-        <v>118</v>
+        <v>111</v>
       </c>
     </row>
     <row r="16">
@@ -4708,13 +4708,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="D16" t="n">
-        <v>98</v>
+        <v>89</v>
       </c>
     </row>
     <row r="17">
@@ -4722,13 +4722,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C17" t="n">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
-        <v>77</v>
+        <v>73</v>
       </c>
     </row>
     <row r="18">
@@ -4736,13 +4736,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C18" t="n">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="D18" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
     </row>
     <row r="19">
@@ -4750,13 +4750,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="D19" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
     </row>
     <row r="20">
@@ -4767,10 +4767,10 @@
         <v>10</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="21">
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C21" t="n">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="D21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5646</v>
+        <v>2054</v>
       </c>
       <c r="C2" t="n">
-        <v>4732</v>
+        <v>10754</v>
       </c>
       <c r="D2" t="n">
-        <v>24685</v>
+        <v>26379</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4045</v>
+        <v>1417</v>
       </c>
       <c r="C3" t="n">
-        <v>2189</v>
+        <v>10182</v>
       </c>
       <c r="D3" t="n">
-        <v>3012</v>
+        <v>5156</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>967</v>
+        <v>258</v>
       </c>
       <c r="C4" t="n">
-        <v>1230</v>
+        <v>5475</v>
       </c>
       <c r="D4" t="n">
-        <v>1549</v>
+        <v>1497</v>
       </c>
     </row>
     <row r="5">
@@ -4865,13 +4865,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="C5" t="n">
-        <v>220</v>
+        <v>209</v>
       </c>
       <c r="D5" t="n">
-        <v>1186</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>183</v>
+        <v>137</v>
       </c>
       <c r="C6" t="n">
-        <v>411</v>
+        <v>341</v>
       </c>
       <c r="D6" t="n">
-        <v>864</v>
+        <v>747</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>161</v>
+        <v>114</v>
       </c>
       <c r="C7" t="n">
-        <v>409</v>
+        <v>321</v>
       </c>
       <c r="D7" t="n">
-        <v>589</v>
+        <v>509</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>115</v>
+        <v>82</v>
       </c>
       <c r="C8" t="n">
-        <v>304</v>
+        <v>244</v>
       </c>
       <c r="D8" t="n">
-        <v>441</v>
+        <v>395</v>
       </c>
     </row>
     <row r="9">
@@ -4921,13 +4921,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>84</v>
+        <v>64</v>
       </c>
       <c r="C9" t="n">
-        <v>233</v>
+        <v>188</v>
       </c>
       <c r="D9" t="n">
-        <v>363</v>
+        <v>322</v>
       </c>
     </row>
     <row r="10">
@@ -4935,13 +4935,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>63</v>
+        <v>48</v>
       </c>
       <c r="C10" t="n">
-        <v>192</v>
+        <v>161</v>
       </c>
       <c r="D10" t="n">
-        <v>352</v>
+        <v>315</v>
       </c>
     </row>
     <row r="11">
@@ -4949,13 +4949,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="C11" t="n">
-        <v>166</v>
+        <v>140</v>
       </c>
       <c r="D11" t="n">
-        <v>270</v>
+        <v>244</v>
       </c>
     </row>
     <row r="12">
@@ -4963,13 +4963,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C12" t="n">
-        <v>134</v>
+        <v>113</v>
       </c>
       <c r="D12" t="n">
-        <v>206</v>
+        <v>187</v>
       </c>
     </row>
     <row r="13">
@@ -4977,13 +4977,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="C13" t="n">
-        <v>103</v>
+        <v>89</v>
       </c>
       <c r="D13" t="n">
-        <v>170</v>
+        <v>155</v>
       </c>
     </row>
     <row r="14">
@@ -4991,13 +4991,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="D14" t="n">
-        <v>148</v>
+        <v>134</v>
       </c>
     </row>
     <row r="15">
@@ -5005,13 +5005,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C15" t="n">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="D15" t="n">
-        <v>120</v>
+        <v>112</v>
       </c>
     </row>
     <row r="16">
@@ -5019,13 +5019,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C16" t="n">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="D16" t="n">
-        <v>98</v>
+        <v>90</v>
       </c>
     </row>
     <row r="17">
@@ -5033,13 +5033,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>73</v>
       </c>
     </row>
     <row r="18">
@@ -5047,13 +5047,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="19">
@@ -5061,13 +5061,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="D19" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
     </row>
     <row r="20">
@@ -5078,10 +5078,10 @@
         <v>9</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="21">
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C21" t="n">
-        <v>106</v>
+        <v>92</v>
       </c>
       <c r="D21" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5837</v>
+        <v>2559</v>
       </c>
       <c r="C2" t="n">
-        <v>3833</v>
+        <v>6689</v>
       </c>
       <c r="D2" t="n">
-        <v>36275</v>
+        <v>24521</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4016</v>
+        <v>1429</v>
       </c>
       <c r="C3" t="n">
-        <v>3095</v>
+        <v>9060</v>
       </c>
       <c r="D3" t="n">
-        <v>6262</v>
+        <v>8341</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2117</v>
+        <v>727</v>
       </c>
       <c r="C4" t="n">
-        <v>1735</v>
+        <v>8117</v>
       </c>
       <c r="D4" t="n">
-        <v>1767</v>
+        <v>2189</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>457</v>
+        <v>156</v>
       </c>
       <c r="C5" t="n">
-        <v>777</v>
+        <v>3187</v>
       </c>
       <c r="D5" t="n">
-        <v>1219</v>
+        <v>1102</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>146</v>
+        <v>111</v>
       </c>
       <c r="C6" t="n">
-        <v>303</v>
+        <v>264</v>
       </c>
       <c r="D6" t="n">
-        <v>910</v>
+        <v>784</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>160</v>
+        <v>117</v>
       </c>
       <c r="C7" t="n">
-        <v>409</v>
+        <v>331</v>
       </c>
       <c r="D7" t="n">
-        <v>625</v>
+        <v>548</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>125</v>
+        <v>90</v>
       </c>
       <c r="C8" t="n">
-        <v>354</v>
+        <v>283</v>
       </c>
       <c r="D8" t="n">
-        <v>462</v>
+        <v>411</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>91</v>
+        <v>66</v>
       </c>
       <c r="C9" t="n">
-        <v>268</v>
+        <v>215</v>
       </c>
       <c r="D9" t="n">
-        <v>372</v>
+        <v>327</v>
       </c>
     </row>
     <row r="10">
@@ -5246,13 +5246,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>66</v>
+        <v>51</v>
       </c>
       <c r="C10" t="n">
-        <v>211</v>
+        <v>173</v>
       </c>
       <c r="D10" t="n">
-        <v>346</v>
+        <v>312</v>
       </c>
     </row>
     <row r="11">
@@ -5260,13 +5260,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="C11" t="n">
-        <v>177</v>
+        <v>149</v>
       </c>
       <c r="D11" t="n">
-        <v>280</v>
+        <v>252</v>
       </c>
     </row>
     <row r="12">
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="C12" t="n">
-        <v>148</v>
+        <v>124</v>
       </c>
       <c r="D12" t="n">
-        <v>211</v>
+        <v>191</v>
       </c>
     </row>
     <row r="13">
@@ -5288,13 +5288,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="C13" t="n">
-        <v>115</v>
+        <v>99</v>
       </c>
       <c r="D13" t="n">
-        <v>173</v>
+        <v>158</v>
       </c>
     </row>
     <row r="14">
@@ -5302,13 +5302,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="D14" t="n">
-        <v>149</v>
+        <v>135</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C15" t="n">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="D15" t="n">
-        <v>121</v>
+        <v>113</v>
       </c>
     </row>
     <row r="16">
@@ -5330,13 +5330,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C16" t="n">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="D16" t="n">
-        <v>99</v>
+        <v>90</v>
       </c>
     </row>
     <row r="17">
@@ -5344,13 +5344,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>74</v>
       </c>
     </row>
     <row r="18">
@@ -5358,13 +5358,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C18" t="n">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>60</v>
+        <v>56</v>
       </c>
     </row>
     <row r="19">
@@ -5372,13 +5372,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C19" t="n">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="20">
@@ -5389,10 +5389,10 @@
         <v>8</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="21">
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C21" t="n">
-        <v>122</v>
+        <v>106</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5184</v>
+        <v>1547</v>
       </c>
       <c r="C2" t="n">
-        <v>3363</v>
+        <v>8574</v>
       </c>
       <c r="D2" t="n">
-        <v>39224</v>
+        <v>23609</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4008</v>
+        <v>1615</v>
       </c>
       <c r="C3" t="n">
-        <v>3025</v>
+        <v>6790</v>
       </c>
       <c r="D3" t="n">
-        <v>10383</v>
+        <v>10213</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2582</v>
+        <v>918</v>
       </c>
       <c r="C4" t="n">
-        <v>2443</v>
+        <v>8464</v>
       </c>
       <c r="D4" t="n">
-        <v>2516</v>
+        <v>3223</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1066</v>
+        <v>365</v>
       </c>
       <c r="C5" t="n">
+        <v>5693</v>
+      </c>
+      <c r="D5" t="n">
         <v>1266</v>
-      </c>
-      <c r="D5" t="n">
-        <v>1281</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>262</v>
+        <v>121</v>
       </c>
       <c r="C6" t="n">
-        <v>537</v>
+        <v>1776</v>
       </c>
       <c r="D6" t="n">
-        <v>950</v>
+        <v>828</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>145</v>
+        <v>107</v>
       </c>
       <c r="C7" t="n">
-        <v>354</v>
+        <v>296</v>
       </c>
       <c r="D7" t="n">
-        <v>659</v>
+        <v>576</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>129</v>
+        <v>94</v>
       </c>
       <c r="C8" t="n">
-        <v>380</v>
+        <v>306</v>
       </c>
       <c r="D8" t="n">
-        <v>484</v>
+        <v>429</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>98</v>
+        <v>71</v>
       </c>
       <c r="C9" t="n">
-        <v>305</v>
+        <v>246</v>
       </c>
       <c r="D9" t="n">
-        <v>378</v>
+        <v>333</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>70</v>
+        <v>53</v>
       </c>
       <c r="C10" t="n">
-        <v>237</v>
+        <v>191</v>
       </c>
       <c r="D10" t="n">
-        <v>346</v>
+        <v>311</v>
       </c>
     </row>
     <row r="11">
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="C11" t="n">
-        <v>191</v>
+        <v>159</v>
       </c>
       <c r="D11" t="n">
-        <v>284</v>
+        <v>258</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="C12" t="n">
-        <v>160</v>
+        <v>133</v>
       </c>
       <c r="D12" t="n">
-        <v>218</v>
+        <v>195</v>
       </c>
     </row>
     <row r="13">
@@ -5599,13 +5599,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="C13" t="n">
-        <v>127</v>
+        <v>109</v>
       </c>
       <c r="D13" t="n">
-        <v>176</v>
+        <v>160</v>
       </c>
     </row>
     <row r="14">
@@ -5613,13 +5613,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>100</v>
+        <v>86</v>
       </c>
       <c r="D14" t="n">
-        <v>149</v>
+        <v>136</v>
       </c>
     </row>
     <row r="15">
@@ -5627,13 +5627,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>82</v>
+        <v>71</v>
       </c>
       <c r="D15" t="n">
-        <v>123</v>
+        <v>113</v>
       </c>
     </row>
     <row r="16">
@@ -5641,13 +5641,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C16" t="n">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="D16" t="n">
-        <v>99</v>
+        <v>91</v>
       </c>
     </row>
     <row r="17">
@@ -5655,13 +5655,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C17" t="n">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
-        <v>79</v>
+        <v>74</v>
       </c>
     </row>
     <row r="18">
@@ -5669,13 +5669,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C18" t="n">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>61</v>
+        <v>56</v>
       </c>
     </row>
     <row r="19">
@@ -5683,13 +5683,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C19" t="n">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="20">
@@ -5700,10 +5700,10 @@
         <v>7</v>
       </c>
       <c r="C20" t="n">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="21">
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C21" t="n">
-        <v>137</v>
+        <v>119</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6252</v>
+        <v>1262</v>
       </c>
       <c r="C2" t="n">
-        <v>7142</v>
+        <v>9906</v>
       </c>
       <c r="D2" t="n">
-        <v>45757</v>
+        <v>27229</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3350</v>
+        <v>1327</v>
       </c>
       <c r="C3" t="n">
-        <v>2620</v>
+        <v>6699</v>
       </c>
       <c r="D3" t="n">
-        <v>13203</v>
+        <v>11439</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2058</v>
+        <v>1051</v>
       </c>
       <c r="C4" t="n">
-        <v>2271</v>
+        <v>7354</v>
       </c>
       <c r="D4" t="n">
-        <v>3364</v>
+        <v>4332</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>946</v>
+        <v>535</v>
       </c>
       <c r="C5" t="n">
-        <v>1372</v>
+        <v>6957</v>
       </c>
       <c r="D5" t="n">
-        <v>1189</v>
+        <v>1534</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>314</v>
+        <v>205</v>
       </c>
       <c r="C6" t="n">
-        <v>614</v>
+        <v>3637</v>
       </c>
       <c r="D6" t="n">
-        <v>758</v>
+        <v>888</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>90</v>
+        <v>106</v>
       </c>
       <c r="C7" t="n">
-        <v>285</v>
+        <v>992</v>
       </c>
       <c r="D7" t="n">
-        <v>520</v>
+        <v>603</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>58</v>
+        <v>92</v>
       </c>
       <c r="C8" t="n">
-        <v>222</v>
+        <v>298</v>
       </c>
       <c r="D8" t="n">
-        <v>364</v>
+        <v>447</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>45</v>
+        <v>74</v>
       </c>
       <c r="C9" t="n">
-        <v>199</v>
+        <v>272</v>
       </c>
       <c r="D9" t="n">
-        <v>270</v>
+        <v>340</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>31</v>
+        <v>55</v>
       </c>
       <c r="C10" t="n">
-        <v>150</v>
+        <v>214</v>
       </c>
       <c r="D10" t="n">
-        <v>237</v>
+        <v>311</v>
       </c>
     </row>
     <row r="11">
@@ -5882,13 +5882,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="C11" t="n">
-        <v>116</v>
+        <v>170</v>
       </c>
       <c r="D11" t="n">
-        <v>193</v>
+        <v>262</v>
       </c>
     </row>
     <row r="12">
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="C12" t="n">
-        <v>93</v>
+        <v>143</v>
       </c>
       <c r="D12" t="n">
-        <v>149</v>
+        <v>199</v>
       </c>
     </row>
     <row r="13">
@@ -5910,13 +5910,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="C13" t="n">
-        <v>73</v>
+        <v>117</v>
       </c>
       <c r="D13" t="n">
-        <v>116</v>
+        <v>162</v>
       </c>
     </row>
     <row r="14">
@@ -5924,13 +5924,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>57</v>
+        <v>94</v>
       </c>
       <c r="D14" t="n">
-        <v>97</v>
+        <v>136</v>
       </c>
     </row>
     <row r="15">
@@ -5938,13 +5938,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>45</v>
+        <v>75</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>114</v>
       </c>
     </row>
     <row r="16">
@@ -5952,13 +5952,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C16" t="n">
-        <v>38</v>
+        <v>66</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>92</v>
       </c>
     </row>
     <row r="17">
@@ -5966,13 +5966,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C17" t="n">
-        <v>35</v>
+        <v>62</v>
       </c>
       <c r="D17" t="n">
-        <v>50</v>
+        <v>74</v>
       </c>
     </row>
     <row r="18">
@@ -5980,13 +5980,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>57</v>
       </c>
     </row>
     <row r="19">
@@ -5994,13 +5994,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>40</v>
       </c>
     </row>
     <row r="20">
@@ -6008,13 +6008,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
     </row>
     <row r="21">
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>76</v>
+        <v>131</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4933</v>
+        <v>2407</v>
       </c>
       <c r="C2" t="n">
-        <v>8692</v>
+        <v>8261</v>
       </c>
       <c r="D2" t="n">
-        <v>43011</v>
+        <v>26744</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4013</v>
+        <v>1080</v>
       </c>
       <c r="C3" t="n">
-        <v>4562</v>
+        <v>7162</v>
       </c>
       <c r="D3" t="n">
-        <v>17939</v>
+        <v>12817</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2382</v>
+        <v>1000</v>
       </c>
       <c r="C4" t="n">
-        <v>2438</v>
+        <v>6822</v>
       </c>
       <c r="D4" t="n">
-        <v>5339</v>
+        <v>5360</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1348</v>
+        <v>664</v>
       </c>
       <c r="C5" t="n">
-        <v>1878</v>
+        <v>6995</v>
       </c>
       <c r="D5" t="n">
-        <v>1591</v>
+        <v>1902</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>585</v>
+        <v>307</v>
       </c>
       <c r="C6" t="n">
-        <v>1036</v>
+        <v>5068</v>
       </c>
       <c r="D6" t="n">
-        <v>822</v>
+        <v>975</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>186</v>
+        <v>133</v>
       </c>
       <c r="C7" t="n">
-        <v>475</v>
+        <v>2122</v>
       </c>
       <c r="D7" t="n">
-        <v>561</v>
+        <v>632</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>68</v>
+        <v>90</v>
       </c>
       <c r="C8" t="n">
-        <v>257</v>
+        <v>590</v>
       </c>
       <c r="D8" t="n">
-        <v>389</v>
+        <v>465</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>47</v>
+        <v>74</v>
       </c>
       <c r="C9" t="n">
-        <v>211</v>
+        <v>279</v>
       </c>
       <c r="D9" t="n">
-        <v>281</v>
+        <v>351</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>34</v>
+        <v>57</v>
       </c>
       <c r="C10" t="n">
-        <v>175</v>
+        <v>236</v>
       </c>
       <c r="D10" t="n">
-        <v>240</v>
+        <v>308</v>
       </c>
     </row>
     <row r="11">
@@ -6193,13 +6193,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="C11" t="n">
-        <v>132</v>
+        <v>186</v>
       </c>
       <c r="D11" t="n">
-        <v>198</v>
+        <v>265</v>
       </c>
     </row>
     <row r="12">
@@ -6207,13 +6207,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="C12" t="n">
-        <v>104</v>
+        <v>151</v>
       </c>
       <c r="D12" t="n">
-        <v>152</v>
+        <v>202</v>
       </c>
     </row>
     <row r="13">
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C13" t="n">
-        <v>82</v>
+        <v>125</v>
       </c>
       <c r="D13" t="n">
-        <v>119</v>
+        <v>164</v>
       </c>
     </row>
     <row r="14">
@@ -6235,13 +6235,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>64</v>
+        <v>100</v>
       </c>
       <c r="D14" t="n">
-        <v>98</v>
+        <v>136</v>
       </c>
     </row>
     <row r="15">
@@ -6249,13 +6249,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>115</v>
       </c>
     </row>
     <row r="16">
@@ -6263,13 +6263,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C16" t="n">
-        <v>40</v>
+        <v>68</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>93</v>
       </c>
     </row>
     <row r="17">
@@ -6277,13 +6277,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C17" t="n">
-        <v>36</v>
+        <v>62</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>74</v>
       </c>
     </row>
     <row r="18">
@@ -6291,13 +6291,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>57</v>
       </c>
     </row>
     <row r="19">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>28</v>
+        <v>40</v>
       </c>
     </row>
     <row r="20">
@@ -6319,13 +6319,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
     </row>
     <row r="21">
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>85</v>
+        <v>142</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4289</v>
+        <v>2128</v>
       </c>
       <c r="C2" t="n">
-        <v>6095</v>
+        <v>5353</v>
       </c>
       <c r="D2" t="n">
-        <v>35673</v>
+        <v>21550</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3682</v>
+        <v>1569</v>
       </c>
       <c r="C3" t="n">
-        <v>5923</v>
+        <v>10685</v>
       </c>
       <c r="D3" t="n">
-        <v>20658</v>
+        <v>13692</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2764</v>
+        <v>613</v>
       </c>
       <c r="C4" t="n">
-        <v>3610</v>
+        <v>10710</v>
       </c>
       <c r="D4" t="n">
-        <v>7544</v>
+        <v>4898</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1634</v>
+        <v>283</v>
       </c>
       <c r="C5" t="n">
-        <v>2150</v>
+        <v>4966</v>
       </c>
       <c r="D5" t="n">
-        <v>2262</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>882</v>
+        <v>122</v>
       </c>
       <c r="C6" t="n">
-        <v>1466</v>
+        <v>2079</v>
       </c>
       <c r="D6" t="n">
-        <v>950</v>
+        <v>619</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>339</v>
+        <v>83</v>
       </c>
       <c r="C7" t="n">
-        <v>777</v>
+        <v>578</v>
       </c>
       <c r="D7" t="n">
-        <v>595</v>
+        <v>455</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>112</v>
+        <v>68</v>
       </c>
       <c r="C8" t="n">
-        <v>370</v>
+        <v>273</v>
       </c>
       <c r="D8" t="n">
-        <v>415</v>
+        <v>343</v>
       </c>
     </row>
     <row r="9">
@@ -6479,10 +6479,10 @@
         <v>52</v>
       </c>
       <c r="C9" t="n">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="D9" t="n">
-        <v>293</v>
+        <v>301</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C10" t="n">
-        <v>192</v>
+        <v>182</v>
       </c>
       <c r="D10" t="n">
-        <v>244</v>
+        <v>259</v>
       </c>
     </row>
     <row r="11">
@@ -6504,13 +6504,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C11" t="n">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="D11" t="n">
-        <v>202</v>
+        <v>197</v>
       </c>
     </row>
     <row r="12">
@@ -6518,13 +6518,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C12" t="n">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="D12" t="n">
-        <v>155</v>
+        <v>160</v>
       </c>
     </row>
     <row r="13">
@@ -6535,10 +6535,10 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="D13" t="n">
-        <v>122</v>
+        <v>133</v>
       </c>
     </row>
     <row r="14">
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C14" t="n">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="D14" t="n">
-        <v>98</v>
+        <v>112</v>
       </c>
     </row>
     <row r="15">
@@ -6560,13 +6560,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C15" t="n">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>91</v>
       </c>
     </row>
     <row r="16">
@@ -6574,13 +6574,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C16" t="n">
-        <v>43</v>
+        <v>60</v>
       </c>
       <c r="D16" t="n">
-        <v>66</v>
+        <v>72</v>
       </c>
     </row>
     <row r="17">
@@ -6588,13 +6588,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C17" t="n">
-        <v>37</v>
+        <v>57</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>55</v>
       </c>
     </row>
     <row r="18">
@@ -6602,10 +6602,10 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>54</v>
       </c>
       <c r="D18" t="n">
         <v>39</v>
@@ -6616,13 +6616,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>52</v>
       </c>
       <c r="D19" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
     </row>
     <row r="20">
@@ -6630,13 +6630,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>142</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21">
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>93</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
